--- a/result/first_infection_DA_2023/04_detached_survival.xlsx
+++ b/result/first_infection_DA_2023/04_detached_survival.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,16 +482,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.264451526493378</v>
+        <v>0.3286267074389452</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F2" t="n">
-        <v>0.264451526493378</v>
+        <v>0.3286267074389452</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45040.41666666666</v>
+        <v>45040.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.08006930323592389</v>
+        <v>0.1517509005737424</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08006930323592389</v>
+        <v>0.1517509005737424</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>45039.66666666666</v>
+        <v>45039.75</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45017.54166666666</v>
+        <v>45015.91666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1018944395822936</v>
+        <v>0.01066020385624379</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1018944395822936</v>
+        <v>0.01066020385624379</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45039.70833333334</v>
+        <v>45038.75</v>
       </c>
     </row>
     <row r="5">
@@ -549,7 +549,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45018.04166666666</v>
+        <v>45017.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8241890302460041</v>
+        <v>0.1046909188464042</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8241890302460041</v>
+        <v>0.1046909188464042</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>45040.625</v>
+        <v>45039.70833333334</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45019</v>
+        <v>45018.04166666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8142138367126522</v>
+        <v>0.8881355561117744</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8142138367126522</v>
+        <v>0.8881355561117744</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>45040.625</v>
@@ -599,7 +599,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45020</v>
+        <v>45019</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7839141863550959</v>
+        <v>0.8656055676210567</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7839141863550959</v>
+        <v>0.8656055676210567</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>45040.625</v>
@@ -624,7 +624,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45021.20833333334</v>
+        <v>45020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -632,16 +632,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7704180204365936</v>
+        <v>0.8358568899928417</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7704180204365936</v>
+        <v>0.8358568899928417</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>45040.58333333334</v>
+        <v>45040.625</v>
       </c>
     </row>
     <row r="9">
@@ -649,7 +649,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45025.70833333334</v>
+        <v>45021.20833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0107658648222532</v>
+        <v>0.7704180204365936</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0107658648222532</v>
+        <v>0.7704180204365936</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>45038.75</v>
+        <v>45040.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -674,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45027.20833333334</v>
+        <v>45025.70833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -682,16 +682,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.923767993334864</v>
+        <v>0.02199181181585527</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>0.923767993334864</v>
+        <v>0.02199181181585527</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>45040.625</v>
+        <v>45039.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +699,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45028.375</v>
+        <v>45027.20833333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3718349210312757</v>
+        <v>0.923767993334864</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3718349210312757</v>
+        <v>0.923767993334864</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>45040.45833333334</v>
+        <v>45040.625</v>
       </c>
     </row>
     <row r="12">
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45029</v>
+        <v>45028.375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7159850436389711</v>
+        <v>0.4113891769452526</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7159850436389711</v>
+        <v>0.4113891769452526</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45040.58333333334</v>
+        <v>45040.5</v>
       </c>
     </row>
     <row r="13">
@@ -749,7 +749,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45030</v>
+        <v>45029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8567889236903758</v>
+        <v>0.8615289531116374</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8567889236903758</v>
+        <v>0.8615289531116374</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>45040.625</v>
@@ -774,7 +774,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45031.125</v>
+        <v>45030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5406350562538148</v>
+        <v>0.8726070393807279</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5406350562538148</v>
+        <v>0.8726070393807279</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45040.54166666666</v>
+        <v>45040.625</v>
       </c>
     </row>
     <row r="15">
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45033</v>
+        <v>45031.125</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5705874151499507</v>
+        <v>0.7893043911162356</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5705874151499507</v>
+        <v>0.7893043911162356</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>45040.54166666666</v>
+        <v>45040.625</v>
       </c>
     </row>
     <row r="16">
@@ -824,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45034</v>
+        <v>45032.58333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7550603207627554</v>
+        <v>0.0578564314299856</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>45034.83333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7550603207627554</v>
+        <v>0.0578564314299856</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>45040.58333333334</v>
+        <v>45039.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -849,7 +849,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45035</v>
+        <v>45033</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7581471794007614</v>
+        <v>0.7990500998486776</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45035.125</v>
+        <v>45034.83333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7581471794007614</v>
+        <v>0.7990500998486776</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>45040.58333333334</v>
+        <v>45040.625</v>
       </c>
     </row>
     <row r="18">
@@ -874,7 +874,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45036.70833333334</v>
+        <v>45034</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01759465481976376</v>
+        <v>0.7791309506412825</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45038.70833333334</v>
+        <v>45034.83333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01759465481976376</v>
+        <v>0.7791309506412825</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>45042.70833333334</v>
+        <v>45040.625</v>
       </c>
     </row>
     <row r="19">
@@ -899,7 +899,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45037.45833333334</v>
+        <v>45035</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -907,16 +907,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1529568517168902</v>
+        <v>0.7581471794007614</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45038.70833333334</v>
+        <v>45035.125</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1529568517168902</v>
+        <v>0.7581471794007614</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>45043.625</v>
+        <v>45040.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -924,7 +924,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45038</v>
+        <v>45036.70833333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3883027323855677</v>
+        <v>0.03138770665627771</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>45038.70833333334</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3883027323855677</v>
+        <v>0.03138770665627771</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>45044.33333333334</v>
+        <v>45043.33333333334</v>
       </c>
     </row>
     <row r="21">
@@ -949,7 +949,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45039</v>
+        <v>45037.45833333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.5599045777057478</v>
+        <v>0.1722542026250431</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45039.58333333334</v>
+        <v>45038.70833333334</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5599045777057478</v>
+        <v>0.1722542026250431</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>45044.75</v>
+        <v>45043.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -974,7 +974,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45044</v>
+        <v>45038</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7816114217717186</v>
+        <v>0.6621118188732632</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45044.95833333334</v>
+        <v>45038.70833333334</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7816114217717186</v>
+        <v>0.6621118188732632</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>45050.625</v>
+        <v>45044.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -999,24 +999,24 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45045</v>
+        <v>45039</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6937569162688637</v>
+        <v>0.7703885826296796</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45045</v>
+        <v>45039.58333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6937569162688637</v>
+        <v>0.7703885826296796</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>45050.625</v>
+        <v>45045.33333333334</v>
       </c>
     </row>
     <row r="24">
@@ -1024,7 +1024,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45048</v>
+        <v>45040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4463706748202665</v>
+        <v>0.717014921196911</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45053.20833333334</v>
+        <v>45040.25</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4463706748202665</v>
+        <v>0.717014921196911</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>45058.45833333334</v>
+        <v>45045.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -1049,7 +1049,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45049</v>
+        <v>45041</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1057,16 +1057,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6731343810115171</v>
+        <v>0.4209447269324219</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45053.20833333334</v>
+        <v>45044.95833333334</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6731343810115171</v>
+        <v>0.4209447269324219</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>45058.54166666666</v>
+        <v>45050.5</v>
       </c>
     </row>
     <row r="26">
@@ -1074,7 +1074,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45050</v>
+        <v>45042.45833333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.7338449283736989</v>
+        <v>0.06613953850598017</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45053.20833333334</v>
+        <v>45044.95833333334</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7338449283736989</v>
+        <v>0.06613953850598017</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>45058.54166666666</v>
+        <v>45049.625</v>
       </c>
     </row>
     <row r="27">
@@ -1099,7 +1099,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45056</v>
+        <v>45043.33333333334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.8183409699875566</v>
+        <v>0.4862631796429971</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45057.25</v>
+        <v>45044.95833333334</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8183409699875566</v>
+        <v>0.4862631796429971</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>45062.58333333334</v>
+        <v>45050.54166666666</v>
       </c>
     </row>
     <row r="28">
@@ -1124,7 +1124,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45057</v>
+        <v>45044</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1132,16 +1132,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7943311960161789</v>
+        <v>0.8672504841013907</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45057.25</v>
+        <v>45044.95833333334</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7943311960161789</v>
+        <v>0.8672504841013907</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>45062.58333333334</v>
+        <v>45050.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -1149,24 +1149,24 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45061.58333333334</v>
+        <v>45045</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.06944073186947104</v>
+        <v>0.7926713901809458</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45064.20833333334</v>
+        <v>45045</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06944073186947104</v>
+        <v>0.7926713901809458</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>45068.58333333334</v>
+        <v>45050.625</v>
       </c>
     </row>
     <row r="30">
@@ -1174,7 +1174,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45062</v>
+        <v>45047.54166666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.7715216479078042</v>
+        <v>0.05577418995150248</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45064.20833333334</v>
+        <v>45053.20833333334</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7715216479078042</v>
+        <v>0.05577418995150248</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>45069.58333333334</v>
+        <v>45057.5</v>
       </c>
     </row>
     <row r="31">
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45063</v>
+        <v>45048</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.6759325444606857</v>
+        <v>0.7870664711710589</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45064.20833333334</v>
+        <v>45053.20833333334</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6759325444606857</v>
+        <v>0.7870664711710589</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>45069.54166666666</v>
+        <v>45058.54166666666</v>
       </c>
     </row>
     <row r="32">
@@ -1224,7 +1224,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45064</v>
+        <v>45049</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.7164646429690098</v>
+        <v>0.8345592687386821</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>45064.20833333334</v>
+        <v>45053.20833333334</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7164646429690098</v>
+        <v>0.8345592687386821</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>45069.58333333334</v>
+        <v>45058.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -1249,7 +1249,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45065.66666666666</v>
+        <v>45050</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0298752885094219</v>
+        <v>0.7629377775008915</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45066</v>
+        <v>45053.20833333334</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0298752885094219</v>
+        <v>0.7629377775008915</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>45070.41666666666</v>
+        <v>45058.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -1274,7 +1274,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45066.375</v>
+        <v>45051</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1282,16 +1282,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3440840089069567</v>
+        <v>0.6804273858161759</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45068.16666666666</v>
+        <v>45053.20833333334</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3440840089069567</v>
+        <v>0.6804273858161759</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>45073.41666666666</v>
+        <v>45058.54166666666</v>
       </c>
     </row>
     <row r="35">
@@ -1299,7 +1299,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45067</v>
+        <v>45052.125</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.3543282485834478</v>
+        <v>0.5739765517908274</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>45068.16666666666</v>
+        <v>45053.20833333334</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3543282485834478</v>
+        <v>0.5739765517908274</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>45073.41666666666</v>
+        <v>45058.5</v>
       </c>
     </row>
     <row r="36">
@@ -1324,7 +1324,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45068</v>
+        <v>45053</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5174058482945865</v>
+        <v>0.6761644805537534</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>45068.16666666666</v>
+        <v>45053.20833333334</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5174058482945865</v>
+        <v>0.6761644805537534</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>45073.5</v>
+        <v>45058.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -1349,7 +1349,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45071.29166666666</v>
+        <v>45055.91666666666</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6978972205447036</v>
+        <v>0.01410477386438957</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>45071.54166666666</v>
+        <v>45057.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6978972205447036</v>
+        <v>0.01410477386438957</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>45077.375</v>
+        <v>45060.70833333334</v>
       </c>
     </row>
     <row r="38">
@@ -1374,7 +1374,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45072</v>
+        <v>45056</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1382,16 +1382,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.5227283033999227</v>
+        <v>0.8937175375651922</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>45074.33333333334</v>
+        <v>45057.25</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5227283033999227</v>
+        <v>0.8937175375651922</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>45079.66666666666</v>
+        <v>45062.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -1399,7 +1399,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45073</v>
+        <v>45057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1407,16 +1407,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.6267559856969777</v>
+        <v>0.7943311960161789</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45074.33333333334</v>
+        <v>45057.25</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6267559856969777</v>
+        <v>0.7943311960161789</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>45079.70833333334</v>
+        <v>45062.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -1424,7 +1424,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45074</v>
+        <v>45058</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.5665742628368845</v>
+        <v>0.5713737731251332</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>45074.33333333334</v>
+        <v>45064.20833333334</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5665742628368845</v>
+        <v>0.5713737731251332</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>45079.70833333334</v>
+        <v>45069.54166666666</v>
       </c>
     </row>
     <row r="41">
@@ -1449,7 +1449,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45075</v>
+        <v>45061.58333333334</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.5655590533169682</v>
+        <v>0.07592783349669273</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>45082.83333333334</v>
+        <v>45064.20833333334</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5655590533169682</v>
+        <v>0.07592783349669273</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>45088.625</v>
+        <v>45068.625</v>
       </c>
     </row>
     <row r="42">
@@ -1474,7 +1474,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45078.58333333334</v>
+        <v>45062</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.258410523939776e-05</v>
+        <v>0.8283534187698821</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>45082.83333333334</v>
+        <v>45064.20833333334</v>
       </c>
       <c r="F42" t="n">
-        <v>9.258410523939776e-05</v>
+        <v>0.8283534187698821</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>45084.75</v>
+        <v>45069.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -1499,24 +1499,24 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45083.125</v>
+        <v>45063</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.6917761456151825</v>
+        <v>0.6926690699636814</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>45083.125</v>
+        <v>45064.20833333334</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6917761456151825</v>
+        <v>0.6926690699636814</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>45088.70833333334</v>
+        <v>45069.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -1524,7 +1524,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45086.33333333334</v>
+        <v>45064</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.4171010984690052</v>
+        <v>0.7398499662233851</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>45090.08333333334</v>
+        <v>45064.20833333334</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4171010984690052</v>
+        <v>0.7398499662233851</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>45095.54166666666</v>
+        <v>45069.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -1549,7 +1549,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45087.45833333334</v>
+        <v>45065.66666666666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1738996025020755</v>
+        <v>0.03209743055873404</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>45090.08333333334</v>
+        <v>45066</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1738996025020755</v>
+        <v>0.03209743055873404</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>45095.375</v>
+        <v>45070.45833333334</v>
       </c>
     </row>
     <row r="46">
@@ -1574,7 +1574,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45088.70833333334</v>
+        <v>45066.375</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1582,16 +1582,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.04025198941890957</v>
+        <v>0.354728370422097</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>45090.08333333334</v>
+        <v>45068.16666666666</v>
       </c>
       <c r="F46" t="n">
-        <v>0.04025198941890957</v>
+        <v>0.354728370422097</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>45094.54166666666</v>
+        <v>45073.41666666666</v>
       </c>
     </row>
     <row r="47">
@@ -1599,7 +1599,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45090.33333333334</v>
+        <v>45067</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1607,16 +1607,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.3817319814351726</v>
+        <v>0.5597540279550377</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>45092.75</v>
+        <v>45068.16666666666</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3817319814351726</v>
+        <v>0.5597540279550377</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>45098.41666666666</v>
+        <v>45073.5</v>
       </c>
     </row>
     <row r="48">
@@ -1624,7 +1624,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45093.41666666666</v>
+        <v>45068</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2173202622756278</v>
+        <v>0.5965773646522328</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>45093.41666666666</v>
+        <v>45068.16666666666</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2173202622756278</v>
+        <v>0.5965773646522328</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>45098.41666666666</v>
+        <v>45073.54166666666</v>
       </c>
     </row>
     <row r="49">
@@ -1649,7 +1649,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45094</v>
+        <v>45069</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1657,16 +1657,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.5182324313187221</v>
+        <v>0.5386904991583538</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>45094.08333333334</v>
+        <v>45069.20833333334</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5182324313187221</v>
+        <v>0.5386904991583538</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>45099.5</v>
+        <v>45074.5</v>
       </c>
     </row>
     <row r="50">
@@ -1674,7 +1674,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45095</v>
+        <v>45070</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1682,16 +1682,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.4815848404668895</v>
+        <v>0.8939151801211785</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>45095.25</v>
+        <v>45071.54166666666</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4815848404668895</v>
+        <v>0.8939151801211785</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>45100.45833333334</v>
+        <v>45077.41666666666</v>
       </c>
     </row>
     <row r="51">
@@ -1699,7 +1699,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45096</v>
+        <v>45071.29166666666</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1707,16 +1707,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.5530270420539736</v>
+        <v>0.7831134797167016</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>45096.66666666666</v>
+        <v>45071.54166666666</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5530270420539736</v>
+        <v>0.7831134797167016</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>45102.33333333334</v>
+        <v>45077.375</v>
       </c>
     </row>
     <row r="52">
@@ -1724,7 +1724,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45097.5</v>
+        <v>45072</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.1102199754905382</v>
+        <v>0.6842290571369254</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>45097.54166666666</v>
+        <v>45074.33333333334</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1102199754905382</v>
+        <v>0.6842290571369254</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>45102.375</v>
+        <v>45079.70833333334</v>
       </c>
     </row>
     <row r="53">
@@ -1749,24 +1749,24 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45098.08333333334</v>
+        <v>45073</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.7462779234901163</v>
+        <v>0.6530968085818081</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>45098.08333333334</v>
+        <v>45074.33333333334</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7462779234901163</v>
+        <v>0.6530968085818081</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>45103.5</v>
+        <v>45079.70833333334</v>
       </c>
     </row>
     <row r="54">
@@ -1774,24 +1774,24 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45099.125</v>
+        <v>45074</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.7745037153369109</v>
+        <v>0.6506418200906873</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>45099.125</v>
+        <v>45074.33333333334</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7745037153369109</v>
+        <v>0.6506418200906873</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>45104.5</v>
+        <v>45079.70833333334</v>
       </c>
     </row>
     <row r="55">
@@ -1799,24 +1799,24 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45100.66666666666</v>
+        <v>45075</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.03278862097539088</v>
+        <v>0.6204240619280972</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>45100.66666666666</v>
+        <v>45082.83333333334</v>
       </c>
       <c r="F55" t="n">
-        <v>0.03278862097539088</v>
+        <v>0.6204240619280972</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>45104.70833333334</v>
+        <v>45088.66666666666</v>
       </c>
     </row>
     <row r="56">
@@ -1824,24 +1824,24 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45103.29166666666</v>
+        <v>45078.58333333334</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.8265334692658969</v>
+        <v>0.002734518641047927</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>45103.29166666666</v>
+        <v>45082.83333333334</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8265334692658969</v>
+        <v>0.002734518641047927</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>45108.625</v>
+        <v>45086.45833333334</v>
       </c>
     </row>
     <row r="57">
@@ -1849,7 +1849,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45104.45833333334</v>
+        <v>45079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1857,16 +1857,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.1708567089189124</v>
+        <v>0.4770436534925134</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45082.83333333334</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1708567089189124</v>
+        <v>0.4770436534925134</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>45126.45833333334</v>
+        <v>45088.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -1874,7 +1874,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45105</v>
+        <v>45080</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1882,16 +1882,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.5961201597826744</v>
+        <v>0.4195132611639111</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45082.83333333334</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5961201597826744</v>
+        <v>0.4195132611639111</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>45126.70833333334</v>
+        <v>45088.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -1899,7 +1899,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45106</v>
+        <v>45081</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1907,16 +1907,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.467984338151005</v>
+        <v>0.3617524818886424</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45082.83333333334</v>
       </c>
       <c r="F59" t="n">
-        <v>0.467984338151005</v>
+        <v>0.3617524818886424</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>45126.66666666666</v>
+        <v>45088.54166666666</v>
       </c>
     </row>
     <row r="60">
@@ -1924,7 +1924,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45107</v>
+        <v>45082</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1932,16 +1932,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.4852637821192718</v>
+        <v>0.5450292989057662</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45082.83333333334</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4852637821192718</v>
+        <v>0.5450292989057662</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>45126.66666666666</v>
+        <v>45088.625</v>
       </c>
     </row>
     <row r="61">
@@ -1949,24 +1949,24 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45108</v>
+        <v>45083.125</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.3733239870827553</v>
+        <v>0.7091857659565337</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45083.125</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3733239870827553</v>
+        <v>0.7091857659565337</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>45126.58333333334</v>
+        <v>45088.70833333334</v>
       </c>
     </row>
     <row r="62">
@@ -1974,7 +1974,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45110</v>
+        <v>45084.5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.3886051083285024</v>
+        <v>0.127832841781612</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45085.41666666666</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3886051083285024</v>
+        <v>0.127832841781612</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>45126.625</v>
+        <v>45090.45833333334</v>
       </c>
     </row>
     <row r="63">
@@ -1999,7 +1999,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45111</v>
+        <v>45085.375</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2007,16 +2007,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.5290365368057712</v>
+        <v>0.3180551046245234</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45085.41666666666</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5290365368057712</v>
+        <v>0.3180551046245234</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>45126.66666666666</v>
+        <v>45090.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -2024,7 +2024,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45112</v>
+        <v>45086.33333333334</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2032,16 +2032,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.5332975194335815</v>
+        <v>0.4698603263405868</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45090.08333333334</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5332975194335815</v>
+        <v>0.4698603263405868</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>45126.66666666666</v>
+        <v>45095.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -2049,7 +2049,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45113</v>
+        <v>45087.45833333334</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2057,16 +2057,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.3529295646553393</v>
+        <v>0.1911109894201827</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45090.08333333334</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3529295646553393</v>
+        <v>0.1911109894201827</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>45126.58333333334</v>
+        <v>45095.41666666666</v>
       </c>
     </row>
     <row r="66">
@@ -2074,7 +2074,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45114</v>
+        <v>45088.70833333334</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2082,16 +2082,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.3670188037218977</v>
+        <v>0.04025198941890957</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45090.08333333334</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3670188037218977</v>
+        <v>0.04025198941890957</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>45126.58333333334</v>
+        <v>45094.54166666666</v>
       </c>
     </row>
     <row r="67">
@@ -2099,7 +2099,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45115</v>
+        <v>45090.33333333334</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2107,16 +2107,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.3321097017409037</v>
+        <v>0.4417808023428184</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45092.75</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3321097017409037</v>
+        <v>0.4417808023428184</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>45126.58333333334</v>
+        <v>45098.41666666666</v>
       </c>
     </row>
     <row r="68">
@@ -2124,7 +2124,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45116</v>
+        <v>45091.41666666666</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.3130445132860514</v>
+        <v>0.2473929241504459</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45092.75</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3130445132860514</v>
+        <v>0.2473929241504459</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>45126.58333333334</v>
+        <v>45098.33333333334</v>
       </c>
     </row>
     <row r="69">
@@ -2149,7 +2149,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45117</v>
+        <v>45092.625</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2157,16 +2157,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.3276178974402142</v>
+        <v>0.05350698348292302</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45092.75</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3276178974402142</v>
+        <v>0.05350698348292302</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>45126.58333333334</v>
+        <v>45097.5</v>
       </c>
     </row>
     <row r="70">
@@ -2174,7 +2174,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45119</v>
+        <v>45093.41666666666</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2182,16 +2182,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.3953635962426745</v>
+        <v>0.2314279133440011</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>45121.29166666666</v>
+        <v>45093.41666666666</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3953635962426745</v>
+        <v>0.2314279133440011</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>45126.625</v>
+        <v>45098.41666666666</v>
       </c>
     </row>
     <row r="71">
@@ -2199,7 +2199,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45122.04166666666</v>
+        <v>45094</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2207,16 +2207,16 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.5184804532445948</v>
+        <v>0.606905353643908</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>45122.04166666666</v>
+        <v>45094.08333333334</v>
       </c>
       <c r="F71" t="n">
-        <v>0.5184804532445948</v>
+        <v>0.606905353643908</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>45127.625</v>
+        <v>45099.5</v>
       </c>
     </row>
     <row r="72">
@@ -2224,7 +2224,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45125</v>
+        <v>45095</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2232,16 +2232,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.3383912729294802</v>
+        <v>0.5900729012000437</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>45125.125</v>
+        <v>45095.25</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3383912729294802</v>
+        <v>0.5900729012000437</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>45130.41666666666</v>
+        <v>45100.5</v>
       </c>
     </row>
     <row r="73">
@@ -2249,7 +2249,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45126</v>
+        <v>45096</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2257,16 +2257,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.7258337623408609</v>
+        <v>0.6224313445914914</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>45126.375</v>
+        <v>45096.66666666666</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7258337623408609</v>
+        <v>0.6224313445914914</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>45131.66666666666</v>
+        <v>45102.33333333334</v>
       </c>
     </row>
     <row r="74">
@@ -2274,24 +2274,24 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45127.58333333334</v>
+        <v>45097.5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.06141189102985795</v>
+        <v>0.1113385840350721</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45127.58333333334</v>
+        <v>45097.54166666666</v>
       </c>
       <c r="F74" t="n">
-        <v>0.06141189102985795</v>
+        <v>0.1113385840350721</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>45132.41666666666</v>
+        <v>45102.375</v>
       </c>
     </row>
     <row r="75">
@@ -2299,24 +2299,24 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45128.45833333334</v>
+        <v>45098.08333333334</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.1603656263270279</v>
+        <v>0.7482475647922768</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>45128.54166666666</v>
+        <v>45098.08333333334</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1603656263270279</v>
+        <v>0.7482475647922768</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>45133.58333333334</v>
+        <v>45103.5</v>
       </c>
     </row>
     <row r="76">
@@ -2324,24 +2324,24 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45129.29166666666</v>
+        <v>45099.125</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.5905167663357545</v>
+        <v>0.7745037153369109</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>45135.58333333334</v>
+        <v>45099.125</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5905167663357545</v>
+        <v>0.7745037153369109</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>45141.375</v>
+        <v>45104.5</v>
       </c>
     </row>
     <row r="77">
@@ -2349,24 +2349,24 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45130</v>
+        <v>45100.66666666666</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.4925105549355235</v>
+        <v>0.03278862097539088</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>45135.58333333334</v>
+        <v>45100.66666666666</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4925105549355235</v>
+        <v>0.03278862097539088</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>45141.33333333334</v>
+        <v>45104.70833333334</v>
       </c>
     </row>
     <row r="78">
@@ -2374,24 +2374,24 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45131</v>
+        <v>45103.29166666666</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.4367093377545327</v>
+        <v>0.8265334692658969</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>45135.58333333334</v>
+        <v>45103.29166666666</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4367093377545327</v>
+        <v>0.8265334692658969</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>45141.33333333334</v>
+        <v>45108.625</v>
       </c>
     </row>
     <row r="79">
@@ -2399,7 +2399,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45133.08333333334</v>
+        <v>45104.45833333334</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.4341490446899824</v>
+        <v>0.1784677424165042</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>45135.58333333334</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4341490446899824</v>
+        <v>0.1784677424165042</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>45141.33333333334</v>
+        <v>45126.45833333334</v>
       </c>
     </row>
     <row r="80">
@@ -2424,7 +2424,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45135.58333333334</v>
+        <v>45105</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.05125426288749041</v>
+        <v>0.685657503775447</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>45135.58333333334</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F80" t="n">
-        <v>0.05125426288749041</v>
+        <v>0.685657503775447</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>45140.375</v>
+        <v>45126.70833333334</v>
       </c>
     </row>
     <row r="81">
@@ -2449,7 +2449,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45137.5</v>
+        <v>45106</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.08845711446832105</v>
+        <v>0.6476909649128586</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>45137.66666666666</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F81" t="n">
-        <v>0.08845711446832105</v>
+        <v>0.6476909649128586</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>45142.54166666666</v>
+        <v>45126.70833333334</v>
       </c>
     </row>
     <row r="82">
@@ -2474,7 +2474,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45138.16666666666</v>
+        <v>45107</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2482,16 +2482,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.6528002445384384</v>
+        <v>0.5737058243592534</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>45138.16666666666</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6528002445384384</v>
+        <v>0.5737058243592534</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>45143.58333333334</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="83">
@@ -2499,7 +2499,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45139.54166666666</v>
+        <v>45108</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.08420418120547568</v>
+        <v>0.4928075363939755</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>45139.75</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F83" t="n">
-        <v>0.08420418120547568</v>
+        <v>0.4928075363939755</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>45144.625</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="84">
@@ -2524,7 +2524,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45140.75</v>
+        <v>45109</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.01720557915300356</v>
+        <v>0.4660188310820785</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>45143.625</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F84" t="n">
-        <v>0.01720557915300356</v>
+        <v>0.4660188310820785</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>45147.58333333334</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="85">
@@ -2549,7 +2549,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45142.41666666666</v>
+        <v>45110</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2557,16 +2557,16 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.2385078335228359</v>
+        <v>0.5229094722504658</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>45143.625</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2385078335228359</v>
+        <v>0.5229094722504658</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>45148.625</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -2574,24 +2574,24 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45143.625</v>
+        <v>45111</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.03891585648216109</v>
+        <v>0.571862002431201</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>45143.625</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F86" t="n">
-        <v>0.03891585648216109</v>
+        <v>0.571862002431201</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>45147.75</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="87">
@@ -2599,7 +2599,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45145.54166666666</v>
+        <v>45112</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.07666762926278607</v>
+        <v>0.5843663813775508</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>45145.54166666666</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F87" t="n">
-        <v>0.07666762926278607</v>
+        <v>0.5843663813775508</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>45150.33333333334</v>
+        <v>45126.70833333334</v>
       </c>
     </row>
     <row r="88">
@@ -2624,7 +2624,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45146.54166666666</v>
+        <v>45113</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2632,16 +2632,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.07973986953517884</v>
+        <v>0.5787128204873239</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>45146.79166666666</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F88" t="n">
-        <v>0.07973986953517884</v>
+        <v>0.5787128204873239</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>45151.625</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="89">
@@ -2649,7 +2649,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45147.625</v>
+        <v>45114</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2657,16 +2657,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0399085373347669</v>
+        <v>0.5082810484433229</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>45149.625</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0399085373347669</v>
+        <v>0.5082810484433229</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>45154.33333333334</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="90">
@@ -2674,24 +2674,24 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45149.625</v>
+        <v>45115</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.04400501987162795</v>
+        <v>0.4438340756000065</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>45149.625</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F90" t="n">
-        <v>0.04400501987162795</v>
+        <v>0.4438340756000065</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>45154.33333333334</v>
+        <v>45126.625</v>
       </c>
     </row>
     <row r="91">
@@ -2699,24 +2699,24 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45153.58333333334</v>
+        <v>45116</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.05789093868140034</v>
+        <v>0.4582923648454913</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>45153.58333333334</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F91" t="n">
-        <v>0.05789093868140034</v>
+        <v>0.4582923648454913</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>45158.33333333334</v>
+        <v>45126.625</v>
       </c>
     </row>
     <row r="92">
@@ -2724,24 +2724,24 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45156.125</v>
+        <v>45117</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.649295716503175</v>
+        <v>0.5073938814270813</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>45156.125</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F92" t="n">
-        <v>0.649295716503175</v>
+        <v>0.5073938814270813</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>45161.54166666666</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="93">
@@ -2749,7 +2749,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45158.75</v>
+        <v>45118</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2757,16 +2757,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.01435951074831754</v>
+        <v>0.4974666295907658</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>45160.33333333334</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F93" t="n">
-        <v>0.01435951074831754</v>
+        <v>0.4974666295907658</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>45163.75</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="94">
@@ -2774,7 +2774,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45159.33333333334</v>
+        <v>45119</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.4421949915088625</v>
+        <v>0.4724760143104735</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>45160.33333333334</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4421949915088625</v>
+        <v>0.4724760143104735</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>45165.45833333334</v>
+        <v>45126.66666666666</v>
       </c>
     </row>
     <row r="95">
@@ -2799,24 +2799,24 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45161.20833333334</v>
+        <v>45120</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.6527214381562265</v>
+        <v>0.4125749372870358</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>45161.20833333334</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F95" t="n">
-        <v>0.6527214381562265</v>
+        <v>0.4125749372870358</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>45166.54166666666</v>
+        <v>45126.625</v>
       </c>
     </row>
     <row r="96">
@@ -2824,7 +2824,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45162.83333333334</v>
+        <v>45121</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2832,16 +2832,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.01411244117018298</v>
+        <v>0.4634936090278413</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>45163.04166666666</v>
+        <v>45121.29166666666</v>
       </c>
       <c r="F96" t="n">
-        <v>0.01411244117018298</v>
+        <v>0.4634936090278413</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>45166.75</v>
+        <v>45126.625</v>
       </c>
     </row>
     <row r="97">
@@ -2849,24 +2849,24 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45163.04166666666</v>
+        <v>45122.04166666666</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.7244698392707946</v>
+        <v>0.6208634042023173</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>45163.04166666666</v>
+        <v>45122.04166666666</v>
       </c>
       <c r="F97" t="n">
-        <v>0.7244698392707946</v>
+        <v>0.6208634042023173</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>45168.58333333334</v>
+        <v>45127.66666666666</v>
       </c>
     </row>
     <row r="98">
@@ -2874,7 +2874,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45164.16666666666</v>
+        <v>45123.375</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2882,16 +2882,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.6015592762313129</v>
+        <v>0.1203669267240603</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>45165.08333333334</v>
+        <v>45125.125</v>
       </c>
       <c r="F98" t="n">
-        <v>0.6015592762313129</v>
+        <v>0.1203669267240603</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>45170.58333333334</v>
+        <v>45129.66666666666</v>
       </c>
     </row>
     <row r="99">
@@ -2899,7 +2899,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45165</v>
+        <v>45125</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2907,16 +2907,16 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.5664526993166028</v>
+        <v>0.7121378607263259</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>45165.08333333334</v>
+        <v>45125.125</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5664526993166028</v>
+        <v>0.7121378607263259</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>45170.58333333334</v>
+        <v>45130.54166666666</v>
       </c>
     </row>
     <row r="100">
@@ -2924,7 +2924,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45166.375</v>
+        <v>45126</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2932,16 +2932,16 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.2955426548071955</v>
+        <v>0.7258337623408609</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>45172.16666666666</v>
+        <v>45126.375</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2955426548071955</v>
+        <v>0.7258337623408609</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>45177.41666666666</v>
+        <v>45131.66666666666</v>
       </c>
     </row>
     <row r="101">
@@ -2949,24 +2949,24 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45174.45833333334</v>
+        <v>45127.58333333334</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.1506919910577908</v>
+        <v>0.06141189102985795</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45177.70833333334</v>
+        <v>45127.58333333334</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1506919910577908</v>
+        <v>0.06141189102985795</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>45182.625</v>
+        <v>45132.41666666666</v>
       </c>
     </row>
     <row r="102">
@@ -2974,7 +2974,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45175.41666666666</v>
+        <v>45128.45833333334</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2982,16 +2982,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.1371045467742358</v>
+        <v>0.160317938402775</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>45177.70833333334</v>
+        <v>45128.54166666666</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1371045467742358</v>
+        <v>0.160317938402775</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>45182.625</v>
+        <v>45133.58333333334</v>
       </c>
     </row>
     <row r="103">
@@ -2999,7 +2999,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45176.45833333334</v>
+        <v>45129.29166666666</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3007,16 +3007,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.1766038224795521</v>
+        <v>0.5954392518930719</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>45177.70833333334</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1766038224795521</v>
+        <v>0.5954392518930719</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>45182.66666666666</v>
+        <v>45141.375</v>
       </c>
     </row>
     <row r="104">
@@ -3024,7 +3024,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45177.70833333334</v>
+        <v>45130</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3032,16 +3032,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.02345241541426114</v>
+        <v>0.5386439628778071</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>45177.70833333334</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="F104" t="n">
-        <v>0.02345241541426114</v>
+        <v>0.5386439628778071</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>45181.75</v>
+        <v>45141.33333333334</v>
       </c>
     </row>
     <row r="105">
@@ -3049,7 +3049,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45178.41666666666</v>
+        <v>45131</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3057,16 +3057,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.2446371047754279</v>
+        <v>0.5143664708222292</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>45183.875</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2446371047754279</v>
+        <v>0.5143664708222292</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>45189.33333333334</v>
+        <v>45141.33333333334</v>
       </c>
     </row>
     <row r="106">
@@ -3074,7 +3074,7 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45179.375</v>
+        <v>45132</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3082,16 +3082,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.3692786480533382</v>
+        <v>0.5024490974189919</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>45183.875</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="F106" t="n">
-        <v>0.3692786480533382</v>
+        <v>0.5024490974189919</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>45189.41666666666</v>
+        <v>45141.33333333334</v>
       </c>
     </row>
     <row r="107">
@@ -3099,7 +3099,7 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45180.375</v>
+        <v>45133.08333333334</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.344284260150898</v>
+        <v>0.5229377236251798</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>45183.875</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="F107" t="n">
-        <v>0.344284260150898</v>
+        <v>0.5229377236251798</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>45189.41666666666</v>
+        <v>45141.33333333334</v>
       </c>
     </row>
     <row r="108">
@@ -3124,7 +3124,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45181.41666666666</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -3132,16 +3132,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.2434031977497781</v>
+        <v>0.05572152211946962</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>45183.875</v>
+        <v>45135.58333333334</v>
       </c>
       <c r="F108" t="n">
-        <v>0.2434031977497781</v>
+        <v>0.05572152211946962</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>45189.33333333334</v>
+        <v>45140.375</v>
       </c>
     </row>
     <row r="109">
@@ -3149,24 +3149,24 @@
         <v>107</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45182.33333333334</v>
+        <v>45136.66666666666</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.4568182417063411</v>
+        <v>0.01931728686724835</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>45183.875</v>
+        <v>45136.66666666666</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4568182417063411</v>
+        <v>0.01931728686724835</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>45189.45833333334</v>
+        <v>45140.70833333334</v>
       </c>
     </row>
     <row r="110">
@@ -3174,7 +3174,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45183</v>
+        <v>45137.5</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -3182,16 +3182,16 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.6233189121674289</v>
+        <v>0.09605864921252411</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>45183.875</v>
+        <v>45137.66666666666</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6233189121674289</v>
+        <v>0.09605864921252411</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>45189.54166666666</v>
+        <v>45142.54166666666</v>
       </c>
     </row>
     <row r="111">
@@ -3199,7 +3199,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45184.41666666666</v>
+        <v>45138.16666666666</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -3207,16 +3207,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.2760537247048586</v>
+        <v>0.6562686342005746</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>45186.54166666666</v>
+        <v>45138.16666666666</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2760537247048586</v>
+        <v>0.6562686342005746</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>45191.58333333334</v>
+        <v>45143.58333333334</v>
       </c>
     </row>
     <row r="112">
@@ -3224,24 +3224,24 @@
         <v>110</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45186.58333333334</v>
+        <v>45139.54166666666</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.06008613200137244</v>
+        <v>0.08420418120547568</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>45186.58333333334</v>
+        <v>45139.75</v>
       </c>
       <c r="F112" t="n">
-        <v>0.06008613200137244</v>
+        <v>0.08420418120547568</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>45191.33333333334</v>
+        <v>45144.625</v>
       </c>
     </row>
     <row r="113">
@@ -3249,7 +3249,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45187.625</v>
+        <v>45140.75</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.04618426022522749</v>
+        <v>0.01721372968531962</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45143.625</v>
       </c>
       <c r="F113" t="n">
-        <v>0.04618426022522749</v>
+        <v>0.01721372968531962</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>45205.58333333334</v>
+        <v>45147.58333333334</v>
       </c>
     </row>
     <row r="114">
@@ -3274,7 +3274,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45188.20833333334</v>
+        <v>45142.41666666666</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.6714665501609469</v>
+        <v>0.2389303509954632</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45143.625</v>
       </c>
       <c r="F114" t="n">
-        <v>0.6714665501609469</v>
+        <v>0.2389303509954632</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>45206.625</v>
+        <v>45148.625</v>
       </c>
     </row>
     <row r="115">
@@ -3299,24 +3299,24 @@
         <v>113</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45189</v>
+        <v>45143.625</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.648567916327826</v>
+        <v>0.03891585648216109</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45143.625</v>
       </c>
       <c r="F115" t="n">
-        <v>0.648567916327826</v>
+        <v>0.03891585648216109</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>45206.625</v>
+        <v>45147.75</v>
       </c>
     </row>
     <row r="116">
@@ -3324,7 +3324,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45191.70833333334</v>
+        <v>45145.54166666666</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -3332,16 +3332,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.02300076133178438</v>
+        <v>0.07666762926278607</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45145.54166666666</v>
       </c>
       <c r="F116" t="n">
-        <v>0.02300076133178438</v>
+        <v>0.07666762926278607</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>45205.41666666666</v>
+        <v>45150.33333333334</v>
       </c>
     </row>
     <row r="117">
@@ -3349,7 +3349,7 @@
         <v>115</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45192.5</v>
+        <v>45146.54166666666</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -3357,16 +3357,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1098140604271629</v>
+        <v>0.08075304655865805</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45146.79166666666</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1098140604271629</v>
+        <v>0.08075304655865805</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>45205.75</v>
+        <v>45151.625</v>
       </c>
     </row>
     <row r="118">
@@ -3374,7 +3374,7 @@
         <v>116</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45194.54166666666</v>
+        <v>45147.625</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -3382,16 +3382,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.08575658882401108</v>
+        <v>0.04017322984771839</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45149.625</v>
       </c>
       <c r="F118" t="n">
-        <v>0.08575658882401108</v>
+        <v>0.04017322984771839</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>45205.70833333334</v>
+        <v>45154.33333333334</v>
       </c>
     </row>
     <row r="119">
@@ -3399,24 +3399,24 @@
         <v>117</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45195.375</v>
+        <v>45149.625</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.3392173070268115</v>
+        <v>0.04412424297431948</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45149.625</v>
       </c>
       <c r="F119" t="n">
-        <v>0.3392173070268115</v>
+        <v>0.04412424297431948</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>45206.5</v>
+        <v>45154.33333333334</v>
       </c>
     </row>
     <row r="120">
@@ -3424,24 +3424,24 @@
         <v>118</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45196.41666666666</v>
+        <v>45153.58333333334</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.2245742327369452</v>
+        <v>0.05825113305052005</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45153.58333333334</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2245742327369452</v>
+        <v>0.05825113305052005</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>45206.41666666666</v>
+        <v>45158.33333333334</v>
       </c>
     </row>
     <row r="121">
@@ -3449,24 +3449,24 @@
         <v>119</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45198.625</v>
+        <v>45156.125</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.04712504193616773</v>
+        <v>0.6496656592785949</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45156.125</v>
       </c>
       <c r="F121" t="n">
-        <v>0.04712504193616773</v>
+        <v>0.6496656592785949</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>45205.58333333334</v>
+        <v>45161.54166666666</v>
       </c>
     </row>
     <row r="122">
@@ -3474,7 +3474,7 @@
         <v>120</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45200.375</v>
+        <v>45158.75</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -3482,16 +3482,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.007757031102490212</v>
+        <v>0.01435951074831754</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>45201.20833333334</v>
+        <v>45160.33333333334</v>
       </c>
       <c r="F122" t="n">
-        <v>0.007757031102490212</v>
+        <v>0.01435951074831754</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>45204.66666666666</v>
+        <v>45163.75</v>
       </c>
     </row>
     <row r="123">
@@ -3499,7 +3499,7 @@
         <v>121</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45201.66666666666</v>
+        <v>45159.33333333334</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -3507,16 +3507,16 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.02932859232025072</v>
+        <v>0.4421949915088625</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>45228.04166666666</v>
+        <v>45160.33333333334</v>
       </c>
       <c r="F123" t="n">
-        <v>0.02932859232025072</v>
+        <v>0.4421949915088625</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>45232.45833333334</v>
+        <v>45165.45833333334</v>
       </c>
     </row>
     <row r="124">
@@ -3524,24 +3524,24 @@
         <v>122</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>45204.125</v>
+        <v>45161.20833333334</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.4614384983268102</v>
+        <v>0.6986763297350767</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>45228.04166666666</v>
+        <v>45161.20833333334</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4614384983268102</v>
+        <v>0.6986763297350767</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>45233.54166666666</v>
+        <v>45166.54166666666</v>
       </c>
     </row>
     <row r="125">
@@ -3549,7 +3549,7 @@
         <v>123</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45214.41666666666</v>
+        <v>45162.83333333334</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -3557,16 +3557,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.1739050065975179</v>
+        <v>0.01468904801849042</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>45228.04166666666</v>
+        <v>45163.04166666666</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1739050065975179</v>
+        <v>0.01468904801849042</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>45233.33333333334</v>
+        <v>45166.75</v>
       </c>
     </row>
     <row r="126">
@@ -3574,24 +3574,24 @@
         <v>124</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45224.70833333334</v>
+        <v>45163.04166666666</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0006307154774340395</v>
+        <v>0.7244698392707946</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>45228.04166666666</v>
+        <v>45163.04166666666</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0006307154774340395</v>
+        <v>0.7244698392707946</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>45230.625</v>
+        <v>45168.58333333334</v>
       </c>
     </row>
     <row r="127">
@@ -3599,7 +3599,7 @@
         <v>125</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45225.79166666666</v>
+        <v>45164.16666666666</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -3607,16 +3607,16 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.01684977786099822</v>
+        <v>0.6224313445914914</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>45228.04166666666</v>
+        <v>45165.08333333334</v>
       </c>
       <c r="F127" t="n">
-        <v>0.01684977786099822</v>
+        <v>0.6224313445914914</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>45232.33333333334</v>
+        <v>45170.58333333334</v>
       </c>
     </row>
     <row r="128">
@@ -3624,7 +3624,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45228.54166666666</v>
+        <v>45165</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -3632,16 +3632,16 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.06723182603082235</v>
+        <v>0.6121261480621042</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>45236.20833333334</v>
+        <v>45165.08333333334</v>
       </c>
       <c r="F128" t="n">
-        <v>0.06723182603082235</v>
+        <v>0.6121261480621042</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>45240.54166666666</v>
+        <v>45170.58333333334</v>
       </c>
     </row>
     <row r="129">
@@ -3649,7 +3649,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45229.45833333334</v>
+        <v>45166.375</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -3657,16 +3657,16 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.1737264177688382</v>
+        <v>0.3468918651892237</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>45236.20833333334</v>
+        <v>45172.16666666666</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1737264177688382</v>
+        <v>0.3468918651892237</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>45240.75</v>
+        <v>45177.45833333334</v>
       </c>
     </row>
     <row r="130">
@@ -3674,7 +3674,7 @@
         <v>128</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45232.54166666666</v>
+        <v>45168.375</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -3682,16 +3682,16 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4.881178496226186e-05</v>
+        <v>0.3066697333517893</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>45236.20833333334</v>
+        <v>45172.16666666666</v>
       </c>
       <c r="F130" t="n">
-        <v>4.881178496226186e-05</v>
+        <v>0.3066697333517893</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>45237.58333333334</v>
+        <v>45177.45833333334</v>
       </c>
     </row>
     <row r="131">
@@ -3699,7 +3699,7 @@
         <v>129</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45233</v>
+        <v>45169.375</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -3707,16 +3707,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.7361270431744097</v>
+        <v>0.2615995273338957</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>45236.20833333334</v>
+        <v>45172.16666666666</v>
       </c>
       <c r="F131" t="n">
-        <v>0.7361270431744097</v>
+        <v>0.2615995273338957</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>45241.54166666666</v>
+        <v>45177.41666666666</v>
       </c>
     </row>
     <row r="132">
@@ -3724,7 +3724,7 @@
         <v>130</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45234.125</v>
+        <v>45170.41666666666</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.7319940893766035</v>
+        <v>0.1854244941808753</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>45236.20833333334</v>
+        <v>45172.16666666666</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7319940893766035</v>
+        <v>0.1854244941808753</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>45241.54166666666</v>
+        <v>45177.33333333334</v>
       </c>
     </row>
     <row r="133">
@@ -3749,7 +3749,7 @@
         <v>131</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45235</v>
+        <v>45172</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -3757,16 +3757,16 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.7581471794007614</v>
+        <v>0.7763751147077492</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>45236.20833333334</v>
+        <v>45172.16666666666</v>
       </c>
       <c r="F133" t="n">
-        <v>0.7581471794007614</v>
+        <v>0.7763751147077492</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>45241.54166666666</v>
+        <v>45177.625</v>
       </c>
     </row>
     <row r="134">
@@ -3774,7 +3774,7 @@
         <v>132</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45236.125</v>
+        <v>45173</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3782,16 +3782,16 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.5361298788414989</v>
+        <v>0.8635899924175149</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>45236.20833333334</v>
+        <v>45173.25</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5361298788414989</v>
+        <v>0.8635899924175149</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>45241.45833333334</v>
+        <v>45178.66666666666</v>
       </c>
     </row>
     <row r="135">
@@ -3799,7 +3799,7 @@
         <v>133</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45238.5</v>
+        <v>45174.45833333334</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3807,16 +3807,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.1202380934609337</v>
+        <v>0.2010923050198854</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>45239.375</v>
+        <v>45177.70833333334</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1202380934609337</v>
+        <v>0.2010923050198854</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>45243.66666666666</v>
+        <v>45182.70833333334</v>
       </c>
     </row>
     <row r="136">
@@ -3824,7 +3824,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>45239.04166666666</v>
+        <v>45175.41666666666</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.849983260921445</v>
+        <v>0.2558940564892063</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>45239.375</v>
+        <v>45177.70833333334</v>
       </c>
       <c r="F136" t="n">
-        <v>0.849983260921445</v>
+        <v>0.2558940564892063</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>45244.58333333334</v>
+        <v>45182.75</v>
       </c>
     </row>
     <row r="137">
@@ -3849,7 +3849,7 @@
         <v>135</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45240.20833333334</v>
+        <v>45176.45833333334</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3857,16 +3857,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.7990500998486776</v>
+        <v>0.1843305745227971</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>45243.375</v>
+        <v>45177.70833333334</v>
       </c>
       <c r="F137" t="n">
-        <v>0.7990500998486776</v>
+        <v>0.1843305745227971</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>45248.58333333334</v>
+        <v>45182.66666666666</v>
       </c>
     </row>
     <row r="138">
@@ -3874,7 +3874,7 @@
         <v>136</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45241</v>
+        <v>45177.70833333334</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3882,16 +3882,16 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.621437721384355</v>
+        <v>0.0239555360101412</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>45243.375</v>
+        <v>45177.70833333334</v>
       </c>
       <c r="F138" t="n">
-        <v>0.621437721384355</v>
+        <v>0.0239555360101412</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>45248.54166666666</v>
+        <v>45181.75</v>
       </c>
     </row>
     <row r="139">
@@ -3899,7 +3899,7 @@
         <v>137</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45245.75</v>
+        <v>45178.41666666666</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -3907,16 +3907,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.00482280766159921</v>
+        <v>0.2563573548314078</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>45266.04166666666</v>
+        <v>45183.875</v>
       </c>
       <c r="F139" t="n">
-        <v>0.00482280766159921</v>
+        <v>0.2563573548314078</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>45269.54166666666</v>
+        <v>45189.375</v>
       </c>
     </row>
     <row r="140">
@@ -3924,7 +3924,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45253.625</v>
+        <v>45179.375</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.03420821836030444</v>
+        <v>0.3720382610486022</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>45266.04166666666</v>
+        <v>45183.875</v>
       </c>
       <c r="F140" t="n">
-        <v>0.03420821836030444</v>
+        <v>0.3720382610486022</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>45270.45833333334</v>
+        <v>45189.41666666666</v>
       </c>
     </row>
     <row r="141">
@@ -3949,7 +3949,7 @@
         <v>139</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45254.5</v>
+        <v>45180.375</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3957,16 +3957,16 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.08696171319376773</v>
+        <v>0.3540900645894658</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>45266.04166666666</v>
+        <v>45183.875</v>
       </c>
       <c r="F141" t="n">
-        <v>0.08696171319376773</v>
+        <v>0.3540900645894658</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>45270.625</v>
+        <v>45189.41666666666</v>
       </c>
     </row>
     <row r="142">
@@ -3974,24 +3974,1174 @@
         <v>140</v>
       </c>
       <c r="B142" s="2" t="n">
+        <v>45181.41666666666</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.2434031977497781</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45183.875</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.2434031977497781</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>45189.33333333334</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>45182.33333333334</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.5404625806451197</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45183.875</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5404625806451197</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>45189.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>45183</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.8883660338527809</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45183.875</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.8883660338527809</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>45189.58333333334</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>45184.41666666666</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.2951005532237448</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45186.54166666666</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.2951005532237448</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>45191.58333333334</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>45186.58333333334</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>rain</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.06068822058170995</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>45186.58333333334</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.06068822058170995</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>45191.33333333334</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>45187.625</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.04618426022522749</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.04618426022522749</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>45205.58333333334</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>45188.20833333334</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.6872347394579964</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.6872347394579964</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>45206.625</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>45189</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.679682646903372</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.679682646903372</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>45206.625</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>45191.70833333334</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.02402022967423574</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.02402022967423574</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>45205.45833333334</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>45192.5</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.1213558223891338</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.1213558223891338</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>45205.75</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>45194.54166666666</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.09368689676360653</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.09368689676360653</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>45205.70833333334</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>45195.375</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.3544746702747428</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.3544746702747428</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>45206.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>45196.41666666666</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.2454473453886319</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.2454473453886319</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>45206.45833333334</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>45198.625</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.04715989138071685</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.04715989138071685</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>45205.58333333334</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>45200.375</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.3308704879120362</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45201.20833333334</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.3308704879120362</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>45206.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>45201.66666666666</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.03207236172702385</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.03207236172702385</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>45232.45833333334</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>45204.125</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.6569591776438988</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.6569591776438988</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>45233.58333333334</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>45212.41666666666</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0.2992511369576356</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.2992511369576356</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>45233.45833333334</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>45213.41666666666</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.2395283839065387</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.2395283839065387</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>45233.41666666666</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>45214.41666666666</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.2675991065579381</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.2675991065579381</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>45233.41666666666</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>45216.75</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.0008272702446923879</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.0008272702446923879</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>45230.66666666666</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>45218</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.8454277149803363</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.8454277149803363</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>45233.625</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>45219</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.5189523842159304</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.5189523842159304</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>45233.54166666666</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>45224.70833333334</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.03169651446403229</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.03169651446403229</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>45232.45833333334</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>45225.79166666666</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0.02529653507165338</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.02529653507165338</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>45232.41666666666</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>45226.66666666666</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.0383228270282464</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.0383228270282464</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>45232.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>45227.20833333334</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.6302772952790135</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45228.04166666666</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.6302772952790135</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>45233.58333333334</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>45228.54166666666</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0.09700997289156472</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45236.20833333334</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.09700997289156472</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>45240.625</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>45229.45833333334</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0.1986257507490876</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45236.20833333334</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.1986257507490876</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>45240.75</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>45232.54166666666</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.002298029748659436</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45236.20833333334</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.002298029748659436</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>45239.375</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>45233</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.8603868639686059</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45236.20833333334</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.8603868639686059</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>45241.58333333334</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>45234.125</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0.8421583287150334</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45236.20833333334</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.8421583287150334</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>45241.54166666666</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>45235</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.8401002062108245</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45236.20833333334</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.8401002062108245</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>45241.54166666666</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>45236.125</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0.8193632212256853</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45236.20833333334</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.8193632212256853</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>45241.54166666666</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>45237.125</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.7369442151515647</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45237.125</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.7369442151515647</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>45242.54166666666</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>45238.5</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.146620141021471</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45239.375</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.146620141021471</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>45243.70833333334</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>45239.04166666666</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.8649387607868022</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45239.375</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.8649387607868022</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>45244.58333333334</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>45240.20833333334</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.8558105793512131</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45243.375</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.8558105793512131</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>45248.58333333334</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>45241</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0.7909005980802465</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45243.375</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.7909005980802465</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>45248.58333333334</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>45245.75</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.00607195760355453</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45266.04166666666</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.00607195760355453</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>45269.625</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>45246</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.3913234768204104</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>45266.04166666666</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.3913234768204104</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>45271.45833333334</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>45253.625</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0.04876857870535003</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>45266.04166666666</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.04876857870535003</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>45270.54166666666</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>45254.5</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0.1046914098264272</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>45266.04166666666</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.1046914098264272</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>45270.66666666666</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>45255.5</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0.1166248937248589</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>45266.04166666666</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.1166248937248589</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>45270.70833333334</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" s="2" t="n">
         <v>45259.54166666666</v>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>0.0008182449989495906</v>
-      </c>
-      <c r="E142" s="2" t="n">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0.08046048441578339</v>
+      </c>
+      <c r="E186" s="2" t="n">
         <v>45266.04166666666</v>
       </c>
-      <c r="F142" t="n">
-        <v>0.0008182449989495906</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>45268.66666666666</v>
+      <c r="F186" t="n">
+        <v>0.08046048441578339</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>45270.625</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0.783014338048681</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>45266.04166666666</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.783014338048681</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>45271.58333333334</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>45264.41666666666</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0.1125785326443946</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45266.04166666666</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.1125785326443946</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>45270.70833333334</v>
       </c>
     </row>
   </sheetData>

--- a/result/first_infection_DA_2023/04_detached_survival.xlsx
+++ b/result/first_infection_DA_2023/04_detached_survival.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yaolinjia/Desktop/Grape/dm_first_inf/result/first_infection_DA_2023/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E4437A-B4D9-D248-867F-3EA32E6A9577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C51CC8-B8BD-C348-A474-D91A7BE9E33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="25600" windowHeight="14840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="25600" windowHeight="14480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -106,12 +106,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,8 +422,13 @@
   <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.1640625" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="22.33203125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="18.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.5" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -445,4303 +455,4303 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>45013</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
         <v>0.32862670743894518</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>0.32862670743894518</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>45040.458333333343</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>45014.416666666657</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2">
         <v>0.15175090057374241</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>0.15175090057374241</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>45039.75</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>45015.916666666657</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2">
         <v>1.0660203856243789E-2</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>1.0660203856243789E-2</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>45038.75</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>45017.541666666657</v>
       </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2">
         <v>0.1046909188464042</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>0.1046909188464042</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>45039.708333333343</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>45018.041666666657</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
         <v>0.88813555611177442</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>0.88813555611177442</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>45019</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2">
         <v>0.86560556762105667</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>0.86560556762105667</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>45020</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2">
         <v>0.83585688999284169</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>0.83585688999284169</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
         <v>45021.208333333343</v>
       </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9">
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2">
         <v>0.77041802043659358</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>0.77041802043659358</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>45040.583333333343</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>45025.708333333343</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2">
         <v>2.1991811815855269E-2</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>2.1991811815855269E-2</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>45039.416666666657</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>45027.208333333343</v>
       </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2">
         <v>0.92376799333486403</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>0.92376799333486403</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>45028.375</v>
       </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2">
         <v>0.41138917694525262</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>0.41138917694525262</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>45040.5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>45029</v>
       </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2">
         <v>0.86152895311163735</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>0.86152895311163735</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>45030</v>
       </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2">
         <v>0.87260703938072792</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>0.87260703938072792</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>45031.125</v>
       </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2">
         <v>0.78930439111623563</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>0.78930439111623563</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>45032.583333333343</v>
       </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2">
         <v>5.7856431429985603E-2</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>5.7856431429985603E-2</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="3">
         <v>45039.583333333343</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>45033</v>
       </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2">
         <v>0.79905009984867759</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>0.79905009984867759</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>45034</v>
       </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2">
         <v>0.77913095064128246</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="3">
         <v>45034.833333333343</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>0.77913095064128246</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="3">
         <v>45040.625</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>45035</v>
       </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2">
         <v>0.75814717940076137</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="3">
         <v>45035.125</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>0.75814717940076137</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="3">
         <v>45040.583333333343</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>45036.708333333343</v>
       </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2">
         <v>3.1387706656277707E-2</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="3">
         <v>45038.708333333343</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>3.1387706656277707E-2</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="3">
         <v>45043.333333333343</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>45037.458333333343</v>
       </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="2">
         <v>0.1722542026250431</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="3">
         <v>45038.708333333343</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>0.1722542026250431</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>45043.666666666657</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="3">
         <v>45038</v>
       </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22">
+      <c r="C22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="2">
         <v>0.6621118188732632</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="3">
         <v>45038.708333333343</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>0.6621118188732632</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="3">
         <v>45044.458333333343</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>45039</v>
       </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23">
+      <c r="C23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2">
         <v>0.77038858262967957</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="3">
         <v>45039.583333333343</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>0.77038858262967957</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="3">
         <v>45045.333333333343</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="A24" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>45040</v>
       </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24">
+      <c r="C24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2">
         <v>0.71701492119691101</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="3">
         <v>45040.25</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>0.71701492119691101</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="3">
         <v>45045.541666666657</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>45041</v>
       </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2">
         <v>0.42094472693242191</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="3">
         <v>45044.958333333343</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>0.42094472693242191</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="3">
         <v>45050.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>45042.458333333343</v>
       </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26">
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="2">
         <v>6.6139538505980172E-2</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="3">
         <v>45044.958333333343</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>6.6139538505980172E-2</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="3">
         <v>45049.625</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>45043.333333333343</v>
       </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27">
+      <c r="C27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="2">
         <v>0.48626317964299709</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="3">
         <v>45044.958333333343</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>0.48626317964299709</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="3">
         <v>45050.541666666657</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="A28" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="3">
         <v>45044</v>
       </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2">
         <v>0.86725048410139072</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="3">
         <v>45044.958333333343</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>0.86725048410139072</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="3">
         <v>45050.666666666657</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="A29" s="2">
         <v>27</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="3">
         <v>45045</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>0.79267139018094579</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="3">
         <v>45045</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>0.79267139018094579</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="3">
         <v>45050.625</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="A30" s="2">
         <v>28</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>45047.541666666657</v>
       </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30">
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="2">
         <v>5.5774189951502483E-2</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="3">
         <v>45053.208333333343</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2">
         <v>5.5774189951502483E-2</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="3">
         <v>45057.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31">
+      <c r="A31" s="2">
         <v>29</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="3">
         <v>45048</v>
       </c>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31">
+      <c r="C31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="2">
         <v>0.78706647117105888</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="3">
         <v>45053.208333333343</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2">
         <v>0.78706647117105888</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>45058.541666666657</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32">
+      <c r="A32" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="3">
         <v>45049</v>
       </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32">
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2">
         <v>0.83455926873868214</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="3">
         <v>45053.208333333343</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2">
         <v>0.83455926873868214</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="3">
         <v>45058.583333333343</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33">
+      <c r="A33" s="2">
         <v>31</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="3">
         <v>45050</v>
       </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33">
+      <c r="C33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="2">
         <v>0.76293777750089153</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="3">
         <v>45053.208333333343</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="2">
         <v>0.76293777750089153</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="3">
         <v>45058.541666666657</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34">
+      <c r="A34" s="2">
         <v>32</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="3">
         <v>45051</v>
       </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34">
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2">
         <v>0.6804273858161759</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="3">
         <v>45053.208333333343</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <v>0.6804273858161759</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="3">
         <v>45058.541666666657</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35">
+      <c r="A35" s="2">
         <v>33</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="3">
         <v>45052.125</v>
       </c>
-      <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35">
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="2">
         <v>0.57397655179082741</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="3">
         <v>45053.208333333343</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <v>0.57397655179082741</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="3">
         <v>45058.5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36">
+      <c r="A36" s="2">
         <v>34</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="3">
         <v>45053</v>
       </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36">
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2">
         <v>0.67616448055375344</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="3">
         <v>45053.208333333343</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <v>0.67616448055375344</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>45058.541666666657</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37">
+      <c r="A37" s="2">
         <v>35</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="3">
         <v>45055.916666666657</v>
       </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37">
+      <c r="C37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="2">
         <v>1.410477386438957E-2</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="3">
         <v>45057.25</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <v>1.410477386438957E-2</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="3">
         <v>45060.708333333343</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38">
+      <c r="A38" s="2">
         <v>36</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="3">
         <v>45056</v>
       </c>
-      <c r="C38" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38">
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2">
         <v>0.89371753756519223</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="3">
         <v>45057.25</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2">
         <v>0.89371753756519223</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="3">
         <v>45062.583333333343</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="A39" s="2">
         <v>37</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="3">
         <v>45057</v>
       </c>
-      <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39">
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="2">
         <v>0.79433119601617885</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="3">
         <v>45057.25</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <v>0.79433119601617885</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="3">
         <v>45062.583333333343</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="A40" s="2">
         <v>38</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="3">
         <v>45058</v>
       </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40">
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2">
         <v>0.57137377312513316</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="3">
         <v>45064.208333333343</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2">
         <v>0.57137377312513316</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="3">
         <v>45069.541666666657</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41">
+      <c r="A41" s="2">
         <v>39</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="3">
         <v>45061.583333333343</v>
       </c>
-      <c r="C41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41">
+      <c r="C41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="2">
         <v>7.5927833496692729E-2</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="3">
         <v>45064.208333333343</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2">
         <v>7.5927833496692729E-2</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="3">
         <v>45068.625</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42">
+      <c r="A42" s="2">
         <v>40</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="3">
         <v>45062</v>
       </c>
-      <c r="C42" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42">
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="2">
         <v>0.82835341876988211</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="3">
         <v>45064.208333333343</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="2">
         <v>0.82835341876988211</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="3">
         <v>45069.583333333343</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43">
+      <c r="A43" s="2">
         <v>41</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="3">
         <v>45063</v>
       </c>
-      <c r="C43" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43">
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="2">
         <v>0.69266906996368138</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="3">
         <v>45064.208333333343</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2">
         <v>0.69266906996368138</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="3">
         <v>45069.583333333343</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44">
+      <c r="A44" s="2">
         <v>42</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="3">
         <v>45064</v>
       </c>
-      <c r="C44" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44">
+      <c r="C44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2">
         <v>0.73984996622338506</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="3">
         <v>45064.208333333343</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2">
         <v>0.73984996622338506</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="3">
         <v>45069.583333333343</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45">
+      <c r="A45" s="2">
         <v>43</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="3">
         <v>45065.666666666657</v>
       </c>
-      <c r="C45" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45">
+      <c r="C45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="2">
         <v>3.2097430558734041E-2</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="3">
         <v>45066</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="2">
         <v>3.2097430558734041E-2</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="3">
         <v>45070.458333333343</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46">
+      <c r="A46" s="2">
         <v>44</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="3">
         <v>45066.375</v>
       </c>
-      <c r="C46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46">
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="2">
         <v>0.35472837042209698</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="3">
         <v>45068.166666666657</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="2">
         <v>0.35472837042209698</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G46" s="3">
         <v>45073.416666666657</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47">
+      <c r="A47" s="2">
         <v>45</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="3">
         <v>45067</v>
       </c>
-      <c r="C47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47">
+      <c r="C47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="2">
         <v>0.5597540279550377</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="3">
         <v>45068.166666666657</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="2">
         <v>0.5597540279550377</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47" s="3">
         <v>45073.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48">
+      <c r="A48" s="2">
         <v>46</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="3">
         <v>45068</v>
       </c>
-      <c r="C48" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48">
+      <c r="C48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="2">
         <v>0.59657736465223277</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="3">
         <v>45068.166666666657</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="2">
         <v>0.59657736465223277</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48" s="3">
         <v>45073.541666666657</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49">
+      <c r="A49" s="2">
         <v>47</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="3">
         <v>45069</v>
       </c>
-      <c r="C49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49">
+      <c r="C49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="2">
         <v>0.53869049915835376</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="3">
         <v>45069.208333333343</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="2">
         <v>0.53869049915835376</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="3">
         <v>45074.5</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50">
+      <c r="A50" s="2">
         <v>48</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="3">
         <v>45070</v>
       </c>
-      <c r="C50" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50">
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2">
         <v>0.89391518012117854</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="3">
         <v>45071.541666666657</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="2">
         <v>0.89391518012117854</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="3">
         <v>45077.416666666657</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51">
+      <c r="A51" s="2">
         <v>49</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="3">
         <v>45071.291666666657</v>
       </c>
-      <c r="C51" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51">
+      <c r="C51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2">
         <v>0.78311347971670164</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="3">
         <v>45071.541666666657</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="2">
         <v>0.78311347971670164</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G51" s="3">
         <v>45077.375</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52">
+      <c r="A52" s="2">
         <v>50</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="3">
         <v>45072</v>
       </c>
-      <c r="C52" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52">
+      <c r="C52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="2">
         <v>0.68422905713692539</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="3">
         <v>45074.333333333343</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="2">
         <v>0.68422905713692539</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G52" s="3">
         <v>45079.708333333343</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53">
+      <c r="A53" s="2">
         <v>51</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="3">
         <v>45073</v>
       </c>
-      <c r="C53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53">
+      <c r="C53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="2">
         <v>0.65309680858180807</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="3">
         <v>45074.333333333343</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="2">
         <v>0.65309680858180807</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G53" s="3">
         <v>45079.708333333343</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54">
+      <c r="A54" s="2">
         <v>52</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="3">
         <v>45074</v>
       </c>
-      <c r="C54" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54">
+      <c r="C54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="2">
         <v>0.65064182009068727</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="3">
         <v>45074.333333333343</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="2">
         <v>0.65064182009068727</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G54" s="3">
         <v>45079.708333333343</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55">
+      <c r="A55" s="2">
         <v>53</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="3">
         <v>45075</v>
       </c>
-      <c r="C55" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55">
+      <c r="C55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="2">
         <v>0.62042406192809718</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="3">
         <v>45082.833333333343</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <v>0.62042406192809718</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G55" s="3">
         <v>45088.666666666657</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56">
+      <c r="A56" s="2">
         <v>54</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="3">
         <v>45078.583333333343</v>
       </c>
-      <c r="C56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56">
+      <c r="C56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="2">
         <v>2.734518641047927E-3</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="3">
         <v>45082.833333333343</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="2">
         <v>2.734518641047927E-3</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="3">
         <v>45086.458333333343</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57">
+      <c r="A57" s="2">
         <v>55</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="3">
         <v>45079</v>
       </c>
-      <c r="C57" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57">
+      <c r="C57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="2">
         <v>0.47704365349251338</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="3">
         <v>45082.833333333343</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="2">
         <v>0.47704365349251338</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G57" s="3">
         <v>45088.583333333343</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58">
+      <c r="A58" s="2">
         <v>56</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="3">
         <v>45080</v>
       </c>
-      <c r="C58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58">
+      <c r="C58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="2">
         <v>0.41951326116391108</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="3">
         <v>45082.833333333343</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="2">
         <v>0.41951326116391108</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G58" s="3">
         <v>45088.583333333343</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59">
+      <c r="A59" s="2">
         <v>57</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="3">
         <v>45081</v>
       </c>
-      <c r="C59" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59">
+      <c r="C59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="2">
         <v>0.3617524818886424</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="3">
         <v>45082.833333333343</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="2">
         <v>0.3617524818886424</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G59" s="3">
         <v>45088.541666666657</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60">
+      <c r="A60" s="2">
         <v>58</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="3">
         <v>45082</v>
       </c>
-      <c r="C60" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60">
+      <c r="C60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="2">
         <v>0.54502929890576624</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="3">
         <v>45082.833333333343</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="2">
         <v>0.54502929890576624</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G60" s="3">
         <v>45088.625</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61">
+      <c r="A61" s="2">
         <v>59</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="3">
         <v>45083.125</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <v>0.70918576595653371</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="3">
         <v>45083.125</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="2">
         <v>0.70918576595653371</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G61" s="3">
         <v>45088.708333333343</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62">
+      <c r="A62" s="2">
         <v>60</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="3">
         <v>45084.5</v>
       </c>
-      <c r="C62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62">
+      <c r="C62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="2">
         <v>0.127832841781612</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="3">
         <v>45085.416666666657</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <v>0.127832841781612</v>
       </c>
-      <c r="G62" s="2">
+      <c r="G62" s="3">
         <v>45090.458333333343</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63">
+      <c r="A63" s="2">
         <v>61</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="3">
         <v>45085.375</v>
       </c>
-      <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63">
+      <c r="C63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="2">
         <v>0.31805510462452341</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="3">
         <v>45085.416666666657</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="2">
         <v>0.31805510462452341</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G63" s="3">
         <v>45090.666666666657</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64">
+      <c r="A64" s="2">
         <v>62</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="3">
         <v>45086.333333333343</v>
       </c>
-      <c r="C64" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64">
+      <c r="C64" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="2">
         <v>0.46986032634058678</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="3">
         <v>45090.083333333343</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="2">
         <v>0.46986032634058678</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G64" s="3">
         <v>45095.583333333343</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65">
+      <c r="A65" s="2">
         <v>63</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="3">
         <v>45087.458333333343</v>
       </c>
-      <c r="C65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65">
+      <c r="C65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="2">
         <v>0.1911109894201827</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="3">
         <v>45090.083333333343</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="2">
         <v>0.1911109894201827</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G65" s="3">
         <v>45095.416666666657</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66">
+      <c r="A66" s="2">
         <v>64</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="3">
         <v>45088.708333333343</v>
       </c>
-      <c r="C66" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66">
+      <c r="C66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="2">
         <v>4.0251989418909569E-2</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="3">
         <v>45090.083333333343</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="2">
         <v>4.0251989418909569E-2</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G66" s="3">
         <v>45094.541666666657</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67">
+      <c r="A67" s="2">
         <v>65</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="3">
         <v>45090.333333333343</v>
       </c>
-      <c r="C67" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67">
+      <c r="C67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="2">
         <v>0.44178080234281841</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="3">
         <v>45092.75</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="2">
         <v>0.44178080234281841</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G67" s="3">
         <v>45098.416666666657</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68">
+      <c r="A68" s="2">
         <v>66</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="3">
         <v>45091.416666666657</v>
       </c>
-      <c r="C68" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68">
+      <c r="C68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="2">
         <v>0.24739292415044589</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="3">
         <v>45092.75</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="2">
         <v>0.24739292415044589</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G68" s="3">
         <v>45098.333333333343</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69">
+      <c r="A69" s="2">
         <v>67</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="3">
         <v>45092.625</v>
       </c>
-      <c r="C69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69">
+      <c r="C69" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="2">
         <v>5.3506983482923022E-2</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="3">
         <v>45092.75</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="2">
         <v>5.3506983482923022E-2</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G69" s="3">
         <v>45097.5</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70">
+      <c r="A70" s="2">
         <v>68</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="3">
         <v>45093.416666666657</v>
       </c>
-      <c r="C70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70">
+      <c r="C70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="2">
         <v>0.23142791334400109</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="3">
         <v>45093.416666666657</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="2">
         <v>0.23142791334400109</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="3">
         <v>45098.416666666657</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71">
+      <c r="A71" s="2">
         <v>69</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="3">
         <v>45094</v>
       </c>
-      <c r="C71" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71">
+      <c r="C71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="2">
         <v>0.60690535364390796</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="3">
         <v>45094.083333333343</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="2">
         <v>0.60690535364390796</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G71" s="3">
         <v>45099.5</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72">
+      <c r="A72" s="2">
         <v>70</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="3">
         <v>45095</v>
       </c>
-      <c r="C72" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72">
+      <c r="C72" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="2">
         <v>0.59007290120004374</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="3">
         <v>45095.25</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="2">
         <v>0.59007290120004374</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G72" s="3">
         <v>45100.5</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73">
+      <c r="A73" s="2">
         <v>71</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="3">
         <v>45096</v>
       </c>
-      <c r="C73" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73">
+      <c r="C73" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="2">
         <v>0.62243134459149141</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="3">
         <v>45096.666666666657</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="2">
         <v>0.62243134459149141</v>
       </c>
-      <c r="G73" s="2">
+      <c r="G73" s="3">
         <v>45102.333333333343</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74">
+      <c r="A74" s="2">
         <v>72</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="3">
         <v>45097.5</v>
       </c>
-      <c r="C74" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74">
+      <c r="C74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="2">
         <v>0.1113385840350721</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="3">
         <v>45097.541666666657</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="2">
         <v>0.1113385840350721</v>
       </c>
-      <c r="G74" s="2">
+      <c r="G74" s="3">
         <v>45102.375</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75">
+      <c r="A75" s="2">
         <v>73</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="3">
         <v>45098.083333333343</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="2">
         <v>0.74824756479227683</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="3">
         <v>45098.083333333343</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="2">
         <v>0.74824756479227683</v>
       </c>
-      <c r="G75" s="2">
+      <c r="G75" s="3">
         <v>45103.5</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76">
+      <c r="A76" s="2">
         <v>74</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="3">
         <v>45099.125</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <v>0.77450371533691087</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="3">
         <v>45099.125</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="2">
         <v>0.77450371533691087</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G76" s="3">
         <v>45104.5</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77">
+      <c r="A77" s="2">
         <v>75</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="3">
         <v>45100.666666666657</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="2">
         <v>3.2788620975390877E-2</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="3">
         <v>45100.666666666657</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="2">
         <v>3.2788620975390877E-2</v>
       </c>
-      <c r="G77" s="2">
+      <c r="G77" s="3">
         <v>45104.708333333343</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78">
+      <c r="A78" s="2">
         <v>76</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="3">
         <v>45103.291666666657</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <v>0.82653346926589688</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="3">
         <v>45103.291666666657</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="2">
         <v>0.82653346926589688</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G78" s="3">
         <v>45108.625</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79">
+      <c r="A79" s="2">
         <v>77</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="3">
         <v>45104.458333333343</v>
       </c>
-      <c r="C79" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79">
+      <c r="C79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="2">
         <v>0.1784677424165042</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="2">
         <v>0.1784677424165042</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G79" s="3">
         <v>45126.458333333343</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80">
+      <c r="A80" s="2">
         <v>78</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="3">
         <v>45105</v>
       </c>
-      <c r="C80" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80">
+      <c r="C80" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="2">
         <v>0.68565750377544699</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="2">
         <v>0.68565750377544699</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G80" s="3">
         <v>45126.708333333343</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81">
+      <c r="A81" s="2">
         <v>79</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="3">
         <v>45106</v>
       </c>
-      <c r="C81" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81">
+      <c r="C81" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="2">
         <v>0.6476909649128586</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="2">
         <v>0.6476909649128586</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G81" s="3">
         <v>45126.708333333343</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82">
+      <c r="A82" s="2">
         <v>80</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="3">
         <v>45107</v>
       </c>
-      <c r="C82" t="s">
-        <v>7</v>
-      </c>
-      <c r="D82">
+      <c r="C82" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="2">
         <v>0.57370582435925344</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="2">
         <v>0.57370582435925344</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G82" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83">
+      <c r="A83" s="2">
         <v>81</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="3">
         <v>45108</v>
       </c>
-      <c r="C83" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83">
+      <c r="C83" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="2">
         <v>0.49280753639397551</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="2">
         <v>0.49280753639397551</v>
       </c>
-      <c r="G83" s="2">
+      <c r="G83" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84">
+      <c r="A84" s="2">
         <v>82</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="3">
         <v>45109</v>
       </c>
-      <c r="C84" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84">
+      <c r="C84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="2">
         <v>0.46601883108207848</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="2">
         <v>0.46601883108207848</v>
       </c>
-      <c r="G84" s="2">
+      <c r="G84" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85">
+      <c r="A85" s="2">
         <v>83</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="3">
         <v>45110</v>
       </c>
-      <c r="C85" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85">
+      <c r="C85" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="2">
         <v>0.5229094722504658</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="2">
         <v>0.5229094722504658</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G85" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86">
+      <c r="A86" s="2">
         <v>84</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="3">
         <v>45111</v>
       </c>
-      <c r="C86" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86">
+      <c r="C86" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="2">
         <v>0.571862002431201</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="2">
         <v>0.571862002431201</v>
       </c>
-      <c r="G86" s="2">
+      <c r="G86" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87">
+      <c r="A87" s="2">
         <v>85</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="3">
         <v>45112</v>
       </c>
-      <c r="C87" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87">
+      <c r="C87" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="2">
         <v>0.58436638137755081</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="2">
         <v>0.58436638137755081</v>
       </c>
-      <c r="G87" s="2">
+      <c r="G87" s="3">
         <v>45126.708333333343</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88">
+      <c r="A88" s="2">
         <v>86</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="3">
         <v>45113</v>
       </c>
-      <c r="C88" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88">
+      <c r="C88" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="2">
         <v>0.57871282048732386</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="2">
         <v>0.57871282048732386</v>
       </c>
-      <c r="G88" s="2">
+      <c r="G88" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89">
+      <c r="A89" s="2">
         <v>87</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="3">
         <v>45114</v>
       </c>
-      <c r="C89" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89">
+      <c r="C89" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="2">
         <v>0.50828104844332289</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="2">
         <v>0.50828104844332289</v>
       </c>
-      <c r="G89" s="2">
+      <c r="G89" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90">
+      <c r="A90" s="2">
         <v>88</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="3">
         <v>45115</v>
       </c>
-      <c r="C90" t="s">
-        <v>7</v>
-      </c>
-      <c r="D90">
+      <c r="C90" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="2">
         <v>0.44383407560000648</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="2">
         <v>0.44383407560000648</v>
       </c>
-      <c r="G90" s="2">
+      <c r="G90" s="3">
         <v>45126.625</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91">
+      <c r="A91" s="2">
         <v>89</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="3">
         <v>45116</v>
       </c>
-      <c r="C91" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91">
+      <c r="C91" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="2">
         <v>0.4582923648454913</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="2">
         <v>0.4582923648454913</v>
       </c>
-      <c r="G91" s="2">
+      <c r="G91" s="3">
         <v>45126.625</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92">
+      <c r="A92" s="2">
         <v>90</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="3">
         <v>45117</v>
       </c>
-      <c r="C92" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92">
+      <c r="C92" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="2">
         <v>0.50739388142708131</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="2">
         <v>0.50739388142708131</v>
       </c>
-      <c r="G92" s="2">
+      <c r="G92" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93">
+      <c r="A93" s="2">
         <v>91</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="3">
         <v>45118</v>
       </c>
-      <c r="C93" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93">
+      <c r="C93" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="2">
         <v>0.49746662959076582</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="2">
         <v>0.49746662959076582</v>
       </c>
-      <c r="G93" s="2">
+      <c r="G93" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94">
+      <c r="A94" s="2">
         <v>92</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="3">
         <v>45119</v>
       </c>
-      <c r="C94" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94">
+      <c r="C94" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="2">
         <v>0.47247601431047348</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="2">
         <v>0.47247601431047348</v>
       </c>
-      <c r="G94" s="2">
+      <c r="G94" s="3">
         <v>45126.666666666657</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95">
+      <c r="A95" s="2">
         <v>93</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="3">
         <v>45120</v>
       </c>
-      <c r="C95" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95">
+      <c r="C95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="2">
         <v>0.41257493728703581</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="2">
         <v>0.41257493728703581</v>
       </c>
-      <c r="G95" s="2">
+      <c r="G95" s="3">
         <v>45126.625</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A96">
+      <c r="A96" s="2">
         <v>94</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="3">
         <v>45121</v>
       </c>
-      <c r="C96" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96">
+      <c r="C96" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="2">
         <v>0.46349360902784131</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="3">
         <v>45121.291666666657</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="2">
         <v>0.46349360902784131</v>
       </c>
-      <c r="G96" s="2">
+      <c r="G96" s="3">
         <v>45126.625</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97">
+      <c r="A97" s="2">
         <v>95</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="3">
         <v>45122.041666666657</v>
       </c>
-      <c r="C97" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97">
+      <c r="C97" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="2">
         <v>0.62086340420231734</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="3">
         <v>45122.041666666657</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="2">
         <v>0.62086340420231734</v>
       </c>
-      <c r="G97" s="2">
+      <c r="G97" s="3">
         <v>45127.666666666657</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98">
+      <c r="A98" s="2">
         <v>96</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="3">
         <v>45123.375</v>
       </c>
-      <c r="C98" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98">
+      <c r="C98" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="2">
         <v>0.1203669267240603</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="3">
         <v>45125.125</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="2">
         <v>0.1203669267240603</v>
       </c>
-      <c r="G98" s="2">
+      <c r="G98" s="3">
         <v>45129.666666666657</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99">
+      <c r="A99" s="2">
         <v>97</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="3">
         <v>45125</v>
       </c>
-      <c r="C99" t="s">
-        <v>7</v>
-      </c>
-      <c r="D99">
+      <c r="C99" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="2">
         <v>0.7121378607263259</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="3">
         <v>45125.125</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="2">
         <v>0.7121378607263259</v>
       </c>
-      <c r="G99" s="2">
+      <c r="G99" s="3">
         <v>45130.541666666657</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100">
+      <c r="A100" s="2">
         <v>98</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="3">
         <v>45126</v>
       </c>
-      <c r="C100" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100">
+      <c r="C100" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="2">
         <v>0.72583376234086094</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="3">
         <v>45126.375</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="2">
         <v>0.72583376234086094</v>
       </c>
-      <c r="G100" s="2">
+      <c r="G100" s="3">
         <v>45131.666666666657</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101">
+      <c r="A101" s="2">
         <v>99</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="3">
         <v>45127.583333333343</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="2">
         <v>6.1411891029857953E-2</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101" s="3">
         <v>45127.583333333343</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="2">
         <v>6.1411891029857953E-2</v>
       </c>
-      <c r="G101" s="2">
+      <c r="G101" s="3">
         <v>45132.416666666657</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102">
+      <c r="A102" s="2">
         <v>100</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="3">
         <v>45128.458333333343</v>
       </c>
-      <c r="C102" t="s">
-        <v>7</v>
-      </c>
-      <c r="D102">
+      <c r="C102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="2">
         <v>0.160317938402775</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="3">
         <v>45128.541666666657</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="2">
         <v>0.160317938402775</v>
       </c>
-      <c r="G102" s="2">
+      <c r="G102" s="3">
         <v>45133.583333333343</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A103">
+      <c r="A103" s="2">
         <v>101</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="3">
         <v>45129.291666666657</v>
       </c>
-      <c r="C103" t="s">
-        <v>7</v>
-      </c>
-      <c r="D103">
+      <c r="C103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="2">
         <v>0.5954392518930719</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="3">
         <v>45135.583333333343</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="2">
         <v>0.5954392518930719</v>
       </c>
-      <c r="G103" s="2">
+      <c r="G103" s="3">
         <v>45141.375</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A104">
+      <c r="A104" s="2">
         <v>102</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="3">
         <v>45130</v>
       </c>
-      <c r="C104" t="s">
-        <v>7</v>
-      </c>
-      <c r="D104">
+      <c r="C104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="2">
         <v>0.53864396287780714</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E104" s="3">
         <v>45135.583333333343</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="2">
         <v>0.53864396287780714</v>
       </c>
-      <c r="G104" s="2">
+      <c r="G104" s="3">
         <v>45141.333333333343</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105">
+      <c r="A105" s="2">
         <v>103</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="3">
         <v>45131</v>
       </c>
-      <c r="C105" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105">
+      <c r="C105" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="2">
         <v>0.51436647082222919</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E105" s="3">
         <v>45135.583333333343</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="2">
         <v>0.51436647082222919</v>
       </c>
-      <c r="G105" s="2">
+      <c r="G105" s="3">
         <v>45141.333333333343</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106">
+      <c r="A106" s="2">
         <v>104</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="3">
         <v>45132</v>
       </c>
-      <c r="C106" t="s">
-        <v>7</v>
-      </c>
-      <c r="D106">
+      <c r="C106" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="2">
         <v>0.50244909741899191</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="3">
         <v>45135.583333333343</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="2">
         <v>0.50244909741899191</v>
       </c>
-      <c r="G106" s="2">
+      <c r="G106" s="3">
         <v>45141.333333333343</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107">
+      <c r="A107" s="2">
         <v>105</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="3">
         <v>45133.083333333343</v>
       </c>
-      <c r="C107" t="s">
-        <v>7</v>
-      </c>
-      <c r="D107">
+      <c r="C107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="2">
         <v>0.52293772362517976</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="3">
         <v>45135.583333333343</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="2">
         <v>0.52293772362517976</v>
       </c>
-      <c r="G107" s="2">
+      <c r="G107" s="3">
         <v>45141.333333333343</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108">
+      <c r="A108" s="2">
         <v>106</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="3">
         <v>45135.583333333343</v>
       </c>
-      <c r="C108" t="s">
-        <v>7</v>
-      </c>
-      <c r="D108">
+      <c r="C108" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" s="2">
         <v>5.5721522119469617E-2</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="3">
         <v>45135.583333333343</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="2">
         <v>5.5721522119469617E-2</v>
       </c>
-      <c r="G108" s="2">
+      <c r="G108" s="3">
         <v>45140.375</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109">
+      <c r="A109" s="2">
         <v>107</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="3">
         <v>45136.666666666657</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <v>1.9317286867248349E-2</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="3">
         <v>45136.666666666657</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="2">
         <v>1.9317286867248349E-2</v>
       </c>
-      <c r="G109" s="2">
+      <c r="G109" s="3">
         <v>45140.708333333343</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110">
+      <c r="A110" s="2">
         <v>108</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="3">
         <v>45137.5</v>
       </c>
-      <c r="C110" t="s">
-        <v>7</v>
-      </c>
-      <c r="D110">
+      <c r="C110" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="2">
         <v>9.6058649212524105E-2</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E110" s="3">
         <v>45137.666666666657</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="2">
         <v>9.6058649212524105E-2</v>
       </c>
-      <c r="G110" s="2">
+      <c r="G110" s="3">
         <v>45142.541666666657</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A111">
+      <c r="A111" s="2">
         <v>109</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="3">
         <v>45138.166666666657</v>
       </c>
-      <c r="C111" t="s">
-        <v>7</v>
-      </c>
-      <c r="D111">
+      <c r="C111" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="2">
         <v>0.65626863420057457</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="3">
         <v>45138.166666666657</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="2">
         <v>0.65626863420057457</v>
       </c>
-      <c r="G111" s="2">
+      <c r="G111" s="3">
         <v>45143.583333333343</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A112">
+      <c r="A112" s="2">
         <v>110</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="3">
         <v>45139.541666666657</v>
       </c>
-      <c r="C112" t="s">
-        <v>7</v>
-      </c>
-      <c r="D112">
+      <c r="C112" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" s="2">
         <v>8.4204181205475681E-2</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="3">
         <v>45139.75</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="2">
         <v>8.4204181205475681E-2</v>
       </c>
-      <c r="G112" s="2">
+      <c r="G112" s="3">
         <v>45144.625</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113">
+      <c r="A113" s="2">
         <v>111</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="3">
         <v>45140.75</v>
       </c>
-      <c r="C113" t="s">
-        <v>7</v>
-      </c>
-      <c r="D113">
+      <c r="C113" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="2">
         <v>1.7213729685319621E-2</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113" s="3">
         <v>45143.625</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="2">
         <v>1.7213729685319621E-2</v>
       </c>
-      <c r="G113" s="2">
+      <c r="G113" s="3">
         <v>45147.583333333343</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114">
+      <c r="A114" s="2">
         <v>112</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="3">
         <v>45142.416666666657</v>
       </c>
-      <c r="C114" t="s">
-        <v>7</v>
-      </c>
-      <c r="D114">
+      <c r="C114" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" s="2">
         <v>0.2389303509954632</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="3">
         <v>45143.625</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="2">
         <v>0.2389303509954632</v>
       </c>
-      <c r="G114" s="2">
+      <c r="G114" s="3">
         <v>45148.625</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115">
+      <c r="A115" s="2">
         <v>113</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="3">
         <v>45143.625</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="2">
         <v>3.8915856482161088E-2</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115" s="3">
         <v>45143.625</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="2">
         <v>3.8915856482161088E-2</v>
       </c>
-      <c r="G115" s="2">
+      <c r="G115" s="3">
         <v>45147.75</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116">
+      <c r="A116" s="2">
         <v>114</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="3">
         <v>45145.541666666657</v>
       </c>
-      <c r="C116" t="s">
-        <v>7</v>
-      </c>
-      <c r="D116">
+      <c r="C116" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" s="2">
         <v>7.6667629262786072E-2</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="3">
         <v>45145.541666666657</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="2">
         <v>7.6667629262786072E-2</v>
       </c>
-      <c r="G116" s="2">
+      <c r="G116" s="3">
         <v>45150.333333333343</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117">
+      <c r="A117" s="2">
         <v>115</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="3">
         <v>45146.541666666657</v>
       </c>
-      <c r="C117" t="s">
-        <v>7</v>
-      </c>
-      <c r="D117">
+      <c r="C117" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" s="2">
         <v>8.0753046558658045E-2</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="3">
         <v>45146.791666666657</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="2">
         <v>8.0753046558658045E-2</v>
       </c>
-      <c r="G117" s="2">
+      <c r="G117" s="3">
         <v>45151.625</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118">
+      <c r="A118" s="2">
         <v>116</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="3">
         <v>45147.625</v>
       </c>
-      <c r="C118" t="s">
-        <v>7</v>
-      </c>
-      <c r="D118">
+      <c r="C118" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" s="2">
         <v>4.0173229847718393E-2</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E118" s="3">
         <v>45149.625</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="2">
         <v>4.0173229847718393E-2</v>
       </c>
-      <c r="G118" s="2">
+      <c r="G118" s="3">
         <v>45154.333333333343</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119">
+      <c r="A119" s="2">
         <v>117</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="3">
         <v>45149.625</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="2">
         <v>4.412424297431948E-2</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="3">
         <v>45149.625</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="2">
         <v>4.412424297431948E-2</v>
       </c>
-      <c r="G119" s="2">
+      <c r="G119" s="3">
         <v>45154.333333333343</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120">
+      <c r="A120" s="2">
         <v>118</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="3">
         <v>45153.583333333343</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="2">
         <v>5.825113305052005E-2</v>
       </c>
-      <c r="E120" s="2">
+      <c r="E120" s="3">
         <v>45153.583333333343</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="2">
         <v>5.825113305052005E-2</v>
       </c>
-      <c r="G120" s="2">
+      <c r="G120" s="3">
         <v>45158.333333333343</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121">
+      <c r="A121" s="2">
         <v>119</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="3">
         <v>45156.125</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <v>0.64966565927859488</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="3">
         <v>45156.125</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="2">
         <v>0.64966565927859488</v>
       </c>
-      <c r="G121" s="2">
+      <c r="G121" s="3">
         <v>45161.541666666657</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122">
+      <c r="A122" s="2">
         <v>120</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="3">
         <v>45158.75</v>
       </c>
-      <c r="C122" t="s">
-        <v>7</v>
-      </c>
-      <c r="D122">
+      <c r="C122" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" s="2">
         <v>1.4359510748317541E-2</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E122" s="3">
         <v>45160.333333333343</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="2">
         <v>1.4359510748317541E-2</v>
       </c>
-      <c r="G122" s="2">
+      <c r="G122" s="3">
         <v>45163.75</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123">
+      <c r="A123" s="2">
         <v>121</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="3">
         <v>45159.333333333343</v>
       </c>
-      <c r="C123" t="s">
-        <v>7</v>
-      </c>
-      <c r="D123">
+      <c r="C123" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="2">
         <v>0.44219499150886249</v>
       </c>
-      <c r="E123" s="2">
+      <c r="E123" s="3">
         <v>45160.333333333343</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="2">
         <v>0.44219499150886249</v>
       </c>
-      <c r="G123" s="2">
+      <c r="G123" s="3">
         <v>45165.458333333343</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124">
+      <c r="A124" s="2">
         <v>122</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="3">
         <v>45161.208333333343</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="2">
         <v>0.69867632973507665</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="3">
         <v>45161.208333333343</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="2">
         <v>0.69867632973507665</v>
       </c>
-      <c r="G124" s="2">
+      <c r="G124" s="3">
         <v>45166.541666666657</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125">
+      <c r="A125" s="2">
         <v>123</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="3">
         <v>45162.833333333343</v>
       </c>
-      <c r="C125" t="s">
-        <v>7</v>
-      </c>
-      <c r="D125">
+      <c r="C125" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125" s="2">
         <v>1.4689048018490421E-2</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="3">
         <v>45163.041666666657</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="2">
         <v>1.4689048018490421E-2</v>
       </c>
-      <c r="G125" s="2">
+      <c r="G125" s="3">
         <v>45166.75</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126">
+      <c r="A126" s="2">
         <v>124</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="3">
         <v>45163.041666666657</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="2">
         <v>0.72446983927079456</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="3">
         <v>45163.041666666657</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="2">
         <v>0.72446983927079456</v>
       </c>
-      <c r="G126" s="2">
+      <c r="G126" s="3">
         <v>45168.583333333343</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127">
+      <c r="A127" s="2">
         <v>125</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="3">
         <v>45164.166666666657</v>
       </c>
-      <c r="C127" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127">
+      <c r="C127" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="2">
         <v>0.62243134459149141</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E127" s="3">
         <v>45165.083333333343</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="2">
         <v>0.62243134459149141</v>
       </c>
-      <c r="G127" s="2">
+      <c r="G127" s="3">
         <v>45170.583333333343</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128">
+      <c r="A128" s="2">
         <v>126</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="3">
         <v>45165</v>
       </c>
-      <c r="C128" t="s">
-        <v>7</v>
-      </c>
-      <c r="D128">
+      <c r="C128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="2">
         <v>0.61212614806210419</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="3">
         <v>45165.083333333343</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="2">
         <v>0.61212614806210419</v>
       </c>
-      <c r="G128" s="2">
+      <c r="G128" s="3">
         <v>45170.583333333343</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129">
+      <c r="A129" s="2">
         <v>127</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="3">
         <v>45166.375</v>
       </c>
-      <c r="C129" t="s">
-        <v>7</v>
-      </c>
-      <c r="D129">
+      <c r="C129" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="2">
         <v>0.34689186518922371</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="3">
         <v>45172.166666666657</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="2">
         <v>0.34689186518922371</v>
       </c>
-      <c r="G129" s="2">
+      <c r="G129" s="3">
         <v>45177.458333333343</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130">
+      <c r="A130" s="2">
         <v>128</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="3">
         <v>45168.375</v>
       </c>
-      <c r="C130" t="s">
-        <v>7</v>
-      </c>
-      <c r="D130">
+      <c r="C130" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="2">
         <v>0.30666973335178932</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E130" s="3">
         <v>45172.166666666657</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="2">
         <v>0.30666973335178932</v>
       </c>
-      <c r="G130" s="2">
+      <c r="G130" s="3">
         <v>45177.458333333343</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131">
+      <c r="A131" s="2">
         <v>129</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="3">
         <v>45169.375</v>
       </c>
-      <c r="C131" t="s">
-        <v>7</v>
-      </c>
-      <c r="D131">
+      <c r="C131" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="2">
         <v>0.26159952733389569</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="3">
         <v>45172.166666666657</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="2">
         <v>0.26159952733389569</v>
       </c>
-      <c r="G131" s="2">
+      <c r="G131" s="3">
         <v>45177.416666666657</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132">
+      <c r="A132" s="2">
         <v>130</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="3">
         <v>45170.416666666657</v>
       </c>
-      <c r="C132" t="s">
-        <v>7</v>
-      </c>
-      <c r="D132">
+      <c r="C132" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="2">
         <v>0.18542449418087531</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="3">
         <v>45172.166666666657</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="2">
         <v>0.18542449418087531</v>
       </c>
-      <c r="G132" s="2">
+      <c r="G132" s="3">
         <v>45177.333333333343</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A133">
+      <c r="A133" s="2">
         <v>131</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="3">
         <v>45172</v>
       </c>
-      <c r="C133" t="s">
-        <v>7</v>
-      </c>
-      <c r="D133">
+      <c r="C133" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="2">
         <v>0.77637511470774923</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E133" s="3">
         <v>45172.166666666657</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="2">
         <v>0.77637511470774923</v>
       </c>
-      <c r="G133" s="2">
+      <c r="G133" s="3">
         <v>45177.625</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A134">
+      <c r="A134" s="2">
         <v>132</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="3">
         <v>45173</v>
       </c>
-      <c r="C134" t="s">
-        <v>7</v>
-      </c>
-      <c r="D134">
+      <c r="C134" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="2">
         <v>0.86358999241751488</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="3">
         <v>45173.25</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="2">
         <v>0.86358999241751488</v>
       </c>
-      <c r="G134" s="2">
+      <c r="G134" s="3">
         <v>45178.666666666657</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A135">
+      <c r="A135" s="2">
         <v>133</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="3">
         <v>45174.458333333343</v>
       </c>
-      <c r="C135" t="s">
-        <v>7</v>
-      </c>
-      <c r="D135">
+      <c r="C135" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="2">
         <v>0.2010923050198854</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="3">
         <v>45177.708333333343</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="2">
         <v>0.2010923050198854</v>
       </c>
-      <c r="G135" s="2">
+      <c r="G135" s="3">
         <v>45182.708333333343</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A136">
+      <c r="A136" s="2">
         <v>134</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="3">
         <v>45175.416666666657</v>
       </c>
-      <c r="C136" t="s">
-        <v>7</v>
-      </c>
-      <c r="D136">
+      <c r="C136" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" s="2">
         <v>0.25589405648920632</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="3">
         <v>45177.708333333343</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="2">
         <v>0.25589405648920632</v>
       </c>
-      <c r="G136" s="2">
+      <c r="G136" s="3">
         <v>45182.75</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137">
+      <c r="A137" s="2">
         <v>135</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="3">
         <v>45176.458333333343</v>
       </c>
-      <c r="C137" t="s">
-        <v>7</v>
-      </c>
-      <c r="D137">
+      <c r="C137" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" s="2">
         <v>0.18433057452279711</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="3">
         <v>45177.708333333343</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="2">
         <v>0.18433057452279711</v>
       </c>
-      <c r="G137" s="2">
+      <c r="G137" s="3">
         <v>45182.666666666657</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A138">
+      <c r="A138" s="2">
         <v>136</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="3">
         <v>45177.708333333343</v>
       </c>
-      <c r="C138" t="s">
-        <v>7</v>
-      </c>
-      <c r="D138">
+      <c r="C138" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" s="2">
         <v>2.39555360101412E-2</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E138" s="3">
         <v>45177.708333333343</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="2">
         <v>2.39555360101412E-2</v>
       </c>
-      <c r="G138" s="2">
+      <c r="G138" s="3">
         <v>45181.75</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A139">
+      <c r="A139" s="2">
         <v>137</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="3">
         <v>45178.416666666657</v>
       </c>
-      <c r="C139" t="s">
-        <v>7</v>
-      </c>
-      <c r="D139">
+      <c r="C139" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" s="2">
         <v>0.25635735483140781</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E139" s="3">
         <v>45183.875</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="2">
         <v>0.25635735483140781</v>
       </c>
-      <c r="G139" s="2">
+      <c r="G139" s="3">
         <v>45189.375</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140">
+      <c r="A140" s="2">
         <v>138</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="3">
         <v>45179.375</v>
       </c>
-      <c r="C140" t="s">
-        <v>7</v>
-      </c>
-      <c r="D140">
+      <c r="C140" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="2">
         <v>0.37203826104860221</v>
       </c>
-      <c r="E140" s="2">
+      <c r="E140" s="3">
         <v>45183.875</v>
       </c>
-      <c r="F140">
+      <c r="F140" s="2">
         <v>0.37203826104860221</v>
       </c>
-      <c r="G140" s="2">
+      <c r="G140" s="3">
         <v>45189.416666666657</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141">
+      <c r="A141" s="2">
         <v>139</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="3">
         <v>45180.375</v>
       </c>
-      <c r="C141" t="s">
-        <v>7</v>
-      </c>
-      <c r="D141">
+      <c r="C141" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" s="2">
         <v>0.35409006458946579</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="3">
         <v>45183.875</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="2">
         <v>0.35409006458946579</v>
       </c>
-      <c r="G141" s="2">
+      <c r="G141" s="3">
         <v>45189.416666666657</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A142">
+      <c r="A142" s="2">
         <v>140</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="3">
         <v>45181.416666666657</v>
       </c>
-      <c r="C142" t="s">
-        <v>7</v>
-      </c>
-      <c r="D142">
+      <c r="C142" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" s="2">
         <v>0.24340319774977809</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="3">
         <v>45183.875</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="2">
         <v>0.24340319774977809</v>
       </c>
-      <c r="G142" s="2">
+      <c r="G142" s="3">
         <v>45189.333333333343</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A143">
+      <c r="A143" s="2">
         <v>141</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="3">
         <v>45182.333333333343</v>
       </c>
-      <c r="C143" t="s">
-        <v>7</v>
-      </c>
-      <c r="D143">
+      <c r="C143" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143" s="2">
         <v>0.54046258064511965</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="3">
         <v>45183.875</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="2">
         <v>0.54046258064511965</v>
       </c>
-      <c r="G143" s="2">
+      <c r="G143" s="3">
         <v>45189.5</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144">
+      <c r="A144" s="2">
         <v>142</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="3">
         <v>45183</v>
       </c>
-      <c r="C144" t="s">
-        <v>7</v>
-      </c>
-      <c r="D144">
+      <c r="C144" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" s="2">
         <v>0.8883660338527809</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="3">
         <v>45183.875</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="2">
         <v>0.8883660338527809</v>
       </c>
-      <c r="G144" s="2">
+      <c r="G144" s="3">
         <v>45189.583333333343</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A145">
+      <c r="A145" s="2">
         <v>143</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="3">
         <v>45184.416666666657</v>
       </c>
-      <c r="C145" t="s">
-        <v>7</v>
-      </c>
-      <c r="D145">
+      <c r="C145" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" s="2">
         <v>0.29510055322374479</v>
       </c>
-      <c r="E145" s="2">
+      <c r="E145" s="3">
         <v>45186.541666666657</v>
       </c>
-      <c r="F145">
+      <c r="F145" s="2">
         <v>0.29510055322374479</v>
       </c>
-      <c r="G145" s="2">
+      <c r="G145" s="3">
         <v>45191.583333333343</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A146">
+      <c r="A146" s="2">
         <v>144</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="3">
         <v>45186.583333333343</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="2">
         <v>6.0688220581709952E-2</v>
       </c>
-      <c r="E146" s="2">
+      <c r="E146" s="3">
         <v>45186.583333333343</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="2">
         <v>6.0688220581709952E-2</v>
       </c>
-      <c r="G146" s="2">
+      <c r="G146" s="3">
         <v>45191.333333333343</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A147">
+      <c r="A147" s="2">
         <v>145</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147" s="3">
         <v>45187.625</v>
       </c>
-      <c r="C147" t="s">
-        <v>7</v>
-      </c>
-      <c r="D147">
+      <c r="C147" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" s="2">
         <v>4.6184260225227487E-2</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E147" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="2">
         <v>4.6184260225227487E-2</v>
       </c>
-      <c r="G147" s="2">
+      <c r="G147" s="3">
         <v>45205.583333333343</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A148">
+      <c r="A148" s="2">
         <v>146</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="3">
         <v>45188.208333333343</v>
       </c>
-      <c r="C148" t="s">
-        <v>7</v>
-      </c>
-      <c r="D148">
+      <c r="C148" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148" s="2">
         <v>0.6872347394579964</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="2">
         <v>0.6872347394579964</v>
       </c>
-      <c r="G148" s="2">
+      <c r="G148" s="3">
         <v>45206.625</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A149">
+      <c r="A149" s="2">
         <v>147</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="3">
         <v>45189</v>
       </c>
-      <c r="C149" t="s">
-        <v>7</v>
-      </c>
-      <c r="D149">
+      <c r="C149" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" s="2">
         <v>0.67968264690337199</v>
       </c>
-      <c r="E149" s="2">
+      <c r="E149" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="2">
         <v>0.67968264690337199</v>
       </c>
-      <c r="G149" s="2">
+      <c r="G149" s="3">
         <v>45206.625</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A150">
+      <c r="A150" s="2">
         <v>148</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="3">
         <v>45191.708333333343</v>
       </c>
-      <c r="C150" t="s">
-        <v>7</v>
-      </c>
-      <c r="D150">
+      <c r="C150" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="2">
         <v>2.4020229674235741E-2</v>
       </c>
-      <c r="E150" s="2">
+      <c r="E150" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F150">
+      <c r="F150" s="2">
         <v>2.4020229674235741E-2</v>
       </c>
-      <c r="G150" s="2">
+      <c r="G150" s="3">
         <v>45205.458333333343</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A151">
+      <c r="A151" s="2">
         <v>149</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="3">
         <v>45192.5</v>
       </c>
-      <c r="C151" t="s">
-        <v>7</v>
-      </c>
-      <c r="D151">
+      <c r="C151" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" s="2">
         <v>0.1213558223891338</v>
       </c>
-      <c r="E151" s="2">
+      <c r="E151" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="2">
         <v>0.1213558223891338</v>
       </c>
-      <c r="G151" s="2">
+      <c r="G151" s="3">
         <v>45205.75</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A152">
+      <c r="A152" s="2">
         <v>150</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="3">
         <v>45194.541666666657</v>
       </c>
-      <c r="C152" t="s">
-        <v>7</v>
-      </c>
-      <c r="D152">
+      <c r="C152" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" s="2">
         <v>9.3686896763606531E-2</v>
       </c>
-      <c r="E152" s="2">
+      <c r="E152" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="2">
         <v>9.3686896763606531E-2</v>
       </c>
-      <c r="G152" s="2">
+      <c r="G152" s="3">
         <v>45205.708333333343</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A153">
+      <c r="A153" s="2">
         <v>151</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="3">
         <v>45195.375</v>
       </c>
-      <c r="C153" t="s">
-        <v>7</v>
-      </c>
-      <c r="D153">
+      <c r="C153" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153" s="2">
         <v>0.35447467027474278</v>
       </c>
-      <c r="E153" s="2">
+      <c r="E153" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="2">
         <v>0.35447467027474278</v>
       </c>
-      <c r="G153" s="2">
+      <c r="G153" s="3">
         <v>45206.5</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A154">
+      <c r="A154" s="2">
         <v>152</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154" s="3">
         <v>45196.416666666657</v>
       </c>
-      <c r="C154" t="s">
-        <v>7</v>
-      </c>
-      <c r="D154">
+      <c r="C154" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" s="2">
         <v>0.24544734538863189</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="2">
         <v>0.24544734538863189</v>
       </c>
-      <c r="G154" s="2">
+      <c r="G154" s="3">
         <v>45206.458333333343</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A155">
+      <c r="A155" s="2">
         <v>153</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="3">
         <v>45198.625</v>
       </c>
-      <c r="C155" t="s">
-        <v>7</v>
-      </c>
-      <c r="D155">
+      <c r="C155" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" s="2">
         <v>4.7159891380716849E-2</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="2">
         <v>4.7159891380716849E-2</v>
       </c>
-      <c r="G155" s="2">
+      <c r="G155" s="3">
         <v>45205.583333333343</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A156">
+      <c r="A156" s="2">
         <v>154</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156" s="3">
         <v>45200.375</v>
       </c>
-      <c r="C156" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156">
+      <c r="C156" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="2">
         <v>0.33087048791203622</v>
       </c>
-      <c r="E156" s="2">
+      <c r="E156" s="3">
         <v>45201.208333333343</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="2">
         <v>0.33087048791203622</v>
       </c>
-      <c r="G156" s="2">
+      <c r="G156" s="3">
         <v>45206.5</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A157">
+      <c r="A157" s="2">
         <v>155</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="3">
         <v>45201.666666666657</v>
       </c>
-      <c r="C157" t="s">
-        <v>7</v>
-      </c>
-      <c r="D157">
+      <c r="C157" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" s="2">
         <v>3.2072361727023851E-2</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="2">
         <v>3.2072361727023851E-2</v>
       </c>
-      <c r="G157" s="2">
+      <c r="G157" s="3">
         <v>45232.458333333343</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A158">
+      <c r="A158" s="2">
         <v>156</v>
       </c>
-      <c r="B158" s="2">
+      <c r="B158" s="3">
         <v>45204.125</v>
       </c>
-      <c r="C158" t="s">
-        <v>7</v>
-      </c>
-      <c r="D158">
+      <c r="C158" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158" s="2">
         <v>0.65695917764389877</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="2">
         <v>0.65695917764389877</v>
       </c>
-      <c r="G158" s="2">
+      <c r="G158" s="3">
         <v>45233.583333333343</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A159">
+      <c r="A159" s="2">
         <v>157</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="3">
         <v>45212.416666666657</v>
       </c>
-      <c r="C159" t="s">
-        <v>7</v>
-      </c>
-      <c r="D159">
+      <c r="C159" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" s="2">
         <v>0.29925113695763561</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="2">
         <v>0.29925113695763561</v>
       </c>
-      <c r="G159" s="2">
+      <c r="G159" s="3">
         <v>45233.458333333343</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A160">
+      <c r="A160" s="2">
         <v>158</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160" s="3">
         <v>45213.416666666657</v>
       </c>
-      <c r="C160" t="s">
-        <v>7</v>
-      </c>
-      <c r="D160">
+      <c r="C160" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" s="2">
         <v>0.23952838390653869</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="2">
         <v>0.23952838390653869</v>
       </c>
-      <c r="G160" s="2">
+      <c r="G160" s="3">
         <v>45233.416666666657</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A161">
+      <c r="A161" s="2">
         <v>159</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="3">
         <v>45214.416666666657</v>
       </c>
-      <c r="C161" t="s">
-        <v>7</v>
-      </c>
-      <c r="D161">
+      <c r="C161" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D161" s="2">
         <v>0.26759910655793812</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="2">
         <v>0.26759910655793812</v>
       </c>
-      <c r="G161" s="2">
+      <c r="G161" s="3">
         <v>45233.416666666657</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A162">
+      <c r="A162" s="2">
         <v>160</v>
       </c>
-      <c r="B162" s="2">
+      <c r="B162" s="3">
         <v>45216.75</v>
       </c>
-      <c r="C162" t="s">
-        <v>7</v>
-      </c>
-      <c r="D162">
+      <c r="C162" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" s="2">
         <v>8.2727024469238795E-4</v>
       </c>
-      <c r="E162" s="2">
+      <c r="E162" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="2">
         <v>8.2727024469238795E-4</v>
       </c>
-      <c r="G162" s="2">
+      <c r="G162" s="3">
         <v>45230.666666666657</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A163">
+      <c r="A163" s="2">
         <v>161</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163" s="3">
         <v>45218</v>
       </c>
-      <c r="C163" t="s">
-        <v>7</v>
-      </c>
-      <c r="D163">
+      <c r="C163" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163" s="2">
         <v>0.84542771498033631</v>
       </c>
-      <c r="E163" s="2">
+      <c r="E163" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="2">
         <v>0.84542771498033631</v>
       </c>
-      <c r="G163" s="2">
+      <c r="G163" s="3">
         <v>45233.625</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A164">
+      <c r="A164" s="2">
         <v>162</v>
       </c>
-      <c r="B164" s="2">
+      <c r="B164" s="3">
         <v>45219</v>
       </c>
-      <c r="C164" t="s">
-        <v>7</v>
-      </c>
-      <c r="D164">
+      <c r="C164" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" s="2">
         <v>0.51895238421593037</v>
       </c>
-      <c r="E164" s="2">
+      <c r="E164" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="2">
         <v>0.51895238421593037</v>
       </c>
-      <c r="G164" s="2">
+      <c r="G164" s="3">
         <v>45233.541666666657</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A165">
+      <c r="A165" s="2">
         <v>163</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165" s="3">
         <v>45224.708333333343</v>
       </c>
-      <c r="C165" t="s">
-        <v>7</v>
-      </c>
-      <c r="D165">
+      <c r="C165" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" s="2">
         <v>3.1696514464032287E-2</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="2">
         <v>3.1696514464032287E-2</v>
       </c>
-      <c r="G165" s="2">
+      <c r="G165" s="3">
         <v>45232.458333333343</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A166">
+      <c r="A166" s="2">
         <v>164</v>
       </c>
-      <c r="B166" s="2">
+      <c r="B166" s="3">
         <v>45225.791666666657</v>
       </c>
-      <c r="C166" t="s">
-        <v>7</v>
-      </c>
-      <c r="D166">
+      <c r="C166" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166" s="2">
         <v>2.529653507165338E-2</v>
       </c>
-      <c r="E166" s="2">
+      <c r="E166" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="2">
         <v>2.529653507165338E-2</v>
       </c>
-      <c r="G166" s="2">
+      <c r="G166" s="3">
         <v>45232.416666666657</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A167">
+      <c r="A167" s="2">
         <v>165</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167" s="3">
         <v>45226.666666666657</v>
       </c>
-      <c r="C167" t="s">
-        <v>7</v>
-      </c>
-      <c r="D167">
+      <c r="C167" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="2">
         <v>3.8322827028246402E-2</v>
       </c>
-      <c r="E167" s="2">
+      <c r="E167" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F167">
+      <c r="F167" s="2">
         <v>3.8322827028246402E-2</v>
       </c>
-      <c r="G167" s="2">
+      <c r="G167" s="3">
         <v>45232.5</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A168">
+      <c r="A168" s="2">
         <v>166</v>
       </c>
-      <c r="B168" s="2">
+      <c r="B168" s="3">
         <v>45227.208333333343</v>
       </c>
-      <c r="C168" t="s">
-        <v>7</v>
-      </c>
-      <c r="D168">
+      <c r="C168" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="2">
         <v>0.63027729527901355</v>
       </c>
-      <c r="E168" s="2">
+      <c r="E168" s="3">
         <v>45228.041666666657</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="2">
         <v>0.63027729527901355</v>
       </c>
-      <c r="G168" s="2">
+      <c r="G168" s="3">
         <v>45233.583333333343</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A169">
+      <c r="A169" s="2">
         <v>167</v>
       </c>
-      <c r="B169" s="2">
+      <c r="B169" s="3">
         <v>45228.541666666657</v>
       </c>
-      <c r="C169" t="s">
-        <v>7</v>
-      </c>
-      <c r="D169">
+      <c r="C169" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" s="2">
         <v>9.7009972891564725E-2</v>
       </c>
-      <c r="E169" s="2">
+      <c r="E169" s="3">
         <v>45236.208333333343</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="2">
         <v>9.7009972891564725E-2</v>
       </c>
-      <c r="G169" s="2">
+      <c r="G169" s="3">
         <v>45240.625</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A170">
+      <c r="A170" s="2">
         <v>168</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170" s="3">
         <v>45229.458333333343</v>
       </c>
-      <c r="C170" t="s">
-        <v>7</v>
-      </c>
-      <c r="D170">
+      <c r="C170" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" s="2">
         <v>0.19862575074908759</v>
       </c>
-      <c r="E170" s="2">
+      <c r="E170" s="3">
         <v>45236.208333333343</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="2">
         <v>0.19862575074908759</v>
       </c>
-      <c r="G170" s="2">
+      <c r="G170" s="3">
         <v>45240.75</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A171">
+      <c r="A171" s="2">
         <v>169</v>
       </c>
-      <c r="B171" s="2">
+      <c r="B171" s="3">
         <v>45232.541666666657</v>
       </c>
-      <c r="C171" t="s">
-        <v>7</v>
-      </c>
-      <c r="D171">
+      <c r="C171" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" s="2">
         <v>2.2980297486594361E-3</v>
       </c>
-      <c r="E171" s="2">
+      <c r="E171" s="3">
         <v>45236.208333333343</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="2">
         <v>2.2980297486594361E-3</v>
       </c>
-      <c r="G171" s="2">
+      <c r="G171" s="3">
         <v>45239.375</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A172">
+      <c r="A172" s="2">
         <v>170</v>
       </c>
-      <c r="B172" s="2">
+      <c r="B172" s="3">
         <v>45233</v>
       </c>
-      <c r="C172" t="s">
-        <v>7</v>
-      </c>
-      <c r="D172">
+      <c r="C172" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" s="2">
         <v>0.86038686396860586</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="3">
         <v>45236.208333333343</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="2">
         <v>0.86038686396860586</v>
       </c>
-      <c r="G172" s="2">
+      <c r="G172" s="3">
         <v>45241.583333333343</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A173">
+      <c r="A173" s="2">
         <v>171</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B173" s="3">
         <v>45234.125</v>
       </c>
-      <c r="C173" t="s">
-        <v>7</v>
-      </c>
-      <c r="D173">
+      <c r="C173" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" s="2">
         <v>0.84215832871503338</v>
       </c>
-      <c r="E173" s="2">
+      <c r="E173" s="3">
         <v>45236.208333333343</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="2">
         <v>0.84215832871503338</v>
       </c>
-      <c r="G173" s="2">
+      <c r="G173" s="3">
         <v>45241.541666666657</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A174">
+      <c r="A174" s="2">
         <v>172</v>
       </c>
-      <c r="B174" s="2">
+      <c r="B174" s="3">
         <v>45235</v>
       </c>
-      <c r="C174" t="s">
-        <v>7</v>
-      </c>
-      <c r="D174">
+      <c r="C174" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" s="2">
         <v>0.84010020621082448</v>
       </c>
-      <c r="E174" s="2">
+      <c r="E174" s="3">
         <v>45236.208333333343</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="2">
         <v>0.84010020621082448</v>
       </c>
-      <c r="G174" s="2">
+      <c r="G174" s="3">
         <v>45241.541666666657</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A175">
+      <c r="A175" s="2">
         <v>173</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B175" s="3">
         <v>45236.125</v>
       </c>
-      <c r="C175" t="s">
-        <v>7</v>
-      </c>
-      <c r="D175">
+      <c r="C175" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" s="2">
         <v>0.81936322122568528</v>
       </c>
-      <c r="E175" s="2">
+      <c r="E175" s="3">
         <v>45236.208333333343</v>
       </c>
-      <c r="F175">
+      <c r="F175" s="2">
         <v>0.81936322122568528</v>
       </c>
-      <c r="G175" s="2">
+      <c r="G175" s="3">
         <v>45241.541666666657</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A176">
+      <c r="A176" s="2">
         <v>174</v>
       </c>
-      <c r="B176" s="2">
+      <c r="B176" s="3">
         <v>45237.125</v>
       </c>
-      <c r="C176" t="s">
-        <v>7</v>
-      </c>
-      <c r="D176">
+      <c r="C176" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D176" s="2">
         <v>0.73694421515156472</v>
       </c>
-      <c r="E176" s="2">
+      <c r="E176" s="3">
         <v>45237.125</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="2">
         <v>0.73694421515156472</v>
       </c>
-      <c r="G176" s="2">
+      <c r="G176" s="3">
         <v>45242.541666666657</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A177">
+      <c r="A177" s="2">
         <v>175</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="3">
         <v>45238.5</v>
       </c>
-      <c r="C177" t="s">
-        <v>7</v>
-      </c>
-      <c r="D177">
+      <c r="C177" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" s="2">
         <v>0.146620141021471</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="3">
         <v>45239.375</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="2">
         <v>0.146620141021471</v>
       </c>
-      <c r="G177" s="2">
+      <c r="G177" s="3">
         <v>45243.708333333343</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A178">
+      <c r="A178" s="2">
         <v>176</v>
       </c>
-      <c r="B178" s="2">
+      <c r="B178" s="3">
         <v>45239.041666666657</v>
       </c>
-      <c r="C178" t="s">
-        <v>7</v>
-      </c>
-      <c r="D178">
+      <c r="C178" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178" s="2">
         <v>0.86493876078680221</v>
       </c>
-      <c r="E178" s="2">
+      <c r="E178" s="3">
         <v>45239.375</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="2">
         <v>0.86493876078680221</v>
       </c>
-      <c r="G178" s="2">
+      <c r="G178" s="3">
         <v>45244.583333333343</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A179">
+      <c r="A179" s="2">
         <v>177</v>
       </c>
-      <c r="B179" s="2">
+      <c r="B179" s="3">
         <v>45240.208333333343</v>
       </c>
-      <c r="C179" t="s">
-        <v>7</v>
-      </c>
-      <c r="D179">
+      <c r="C179" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" s="2">
         <v>0.85581057935121307</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="3">
         <v>45243.375</v>
       </c>
-      <c r="F179">
+      <c r="F179" s="2">
         <v>0.85581057935121307</v>
       </c>
-      <c r="G179" s="2">
+      <c r="G179" s="3">
         <v>45248.583333333343</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A180">
+      <c r="A180" s="2">
         <v>178</v>
       </c>
-      <c r="B180" s="2">
+      <c r="B180" s="3">
         <v>45241</v>
       </c>
-      <c r="C180" t="s">
-        <v>7</v>
-      </c>
-      <c r="D180">
+      <c r="C180" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" s="2">
         <v>0.79090059808024649</v>
       </c>
-      <c r="E180" s="2">
+      <c r="E180" s="3">
         <v>45243.375</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="2">
         <v>0.79090059808024649</v>
       </c>
-      <c r="G180" s="2">
+      <c r="G180" s="3">
         <v>45248.583333333343</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A181">
+      <c r="A181" s="2">
         <v>179</v>
       </c>
-      <c r="B181" s="2">
+      <c r="B181" s="3">
         <v>45245.75</v>
       </c>
-      <c r="C181" t="s">
-        <v>7</v>
-      </c>
-      <c r="D181">
+      <c r="C181" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" s="2">
         <v>6.0719576035545304E-3</v>
       </c>
-      <c r="E181" s="2">
+      <c r="E181" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F181">
+      <c r="F181" s="2">
         <v>6.0719576035545304E-3</v>
       </c>
-      <c r="G181" s="2">
+      <c r="G181" s="3">
         <v>45269.625</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A182">
+      <c r="A182" s="2">
         <v>180</v>
       </c>
-      <c r="B182" s="2">
+      <c r="B182" s="3">
         <v>45246</v>
       </c>
-      <c r="C182" t="s">
-        <v>7</v>
-      </c>
-      <c r="D182">
+      <c r="C182" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182" s="2">
         <v>0.39132347682041041</v>
       </c>
-      <c r="E182" s="2">
+      <c r="E182" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="2">
         <v>0.39132347682041041</v>
       </c>
-      <c r="G182" s="2">
+      <c r="G182" s="3">
         <v>45271.458333333343</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A183">
+      <c r="A183" s="2">
         <v>181</v>
       </c>
-      <c r="B183" s="2">
+      <c r="B183" s="3">
         <v>45253.625</v>
       </c>
-      <c r="C183" t="s">
-        <v>7</v>
-      </c>
-      <c r="D183">
+      <c r="C183" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" s="2">
         <v>4.8768578705350028E-2</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="2">
         <v>4.8768578705350028E-2</v>
       </c>
-      <c r="G183" s="2">
+      <c r="G183" s="3">
         <v>45270.541666666657</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A184">
+      <c r="A184" s="2">
         <v>182</v>
       </c>
-      <c r="B184" s="2">
+      <c r="B184" s="3">
         <v>45254.5</v>
       </c>
-      <c r="C184" t="s">
-        <v>7</v>
-      </c>
-      <c r="D184">
+      <c r="C184" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" s="2">
         <v>0.1046914098264272</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="2">
         <v>0.1046914098264272</v>
       </c>
-      <c r="G184" s="2">
+      <c r="G184" s="3">
         <v>45270.666666666657</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A185">
+      <c r="A185" s="2">
         <v>183</v>
       </c>
-      <c r="B185" s="2">
+      <c r="B185" s="3">
         <v>45255.5</v>
       </c>
-      <c r="C185" t="s">
-        <v>7</v>
-      </c>
-      <c r="D185">
+      <c r="C185" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185" s="2">
         <v>0.1166248937248589</v>
       </c>
-      <c r="E185" s="2">
+      <c r="E185" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="2">
         <v>0.1166248937248589</v>
       </c>
-      <c r="G185" s="2">
+      <c r="G185" s="3">
         <v>45270.708333333343</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A186">
+      <c r="A186" s="2">
         <v>184</v>
       </c>
-      <c r="B186" s="2">
+      <c r="B186" s="3">
         <v>45259.541666666657</v>
       </c>
-      <c r="C186" t="s">
-        <v>7</v>
-      </c>
-      <c r="D186">
+      <c r="C186" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186" s="2">
         <v>8.0460484415783393E-2</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="2">
         <v>8.0460484415783393E-2</v>
       </c>
-      <c r="G186" s="2">
+      <c r="G186" s="3">
         <v>45270.625</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A187">
+      <c r="A187" s="2">
         <v>185</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="3">
         <v>45260</v>
       </c>
-      <c r="C187" t="s">
-        <v>7</v>
-      </c>
-      <c r="D187">
+      <c r="C187" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" s="2">
         <v>0.78301433804868104</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="2">
         <v>0.78301433804868104</v>
       </c>
-      <c r="G187" s="2">
+      <c r="G187" s="3">
         <v>45271.583333333343</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A188">
+      <c r="A188" s="2">
         <v>186</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188" s="3">
         <v>45264.416666666657</v>
       </c>
-      <c r="C188" t="s">
-        <v>7</v>
-      </c>
-      <c r="D188">
+      <c r="C188" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188" s="2">
         <v>0.1125785326443946</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="3">
         <v>45266.041666666657</v>
       </c>
-      <c r="F188">
+      <c r="F188" s="2">
         <v>0.1125785326443946</v>
       </c>
-      <c r="G188" s="2">
+      <c r="G188" s="3">
         <v>45270.708333333343</v>
       </c>
     </row>
